--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -638,22 +638,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -638,22 +638,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2168,16 +2168,16 @@
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2168,16 +2168,16 @@
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2168,16 +2168,16 @@
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL17"/>
+  <dimension ref="A1:AL20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2300,16 +2300,16 @@
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="AL14" s="3" t="n">
-        <v>45883.83333333334</v>
+        <v>45883.79166666666</v>
       </c>
     </row>
     <row r="15">
@@ -2349,12 +2349,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="AL15" s="3" t="n">
-        <v>45883.89583333334</v>
+        <v>45883.79166666666</v>
       </c>
     </row>
     <row r="16">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="AL16" s="3" t="n">
-        <v>45883.89583333334</v>
+        <v>45883.79166666666</v>
       </c>
     </row>
     <row r="17">
@@ -2613,129 +2613,525 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Inter Miami II</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Huntsville City</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL17" s="3" t="n">
+        <v>45883.83333333334</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>45883</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Universitario</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL18" s="3" t="n">
+        <v>45883.89583333334</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>45883</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL19" s="3" t="n">
+        <v>45883.89583333334</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>45883</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>21:35</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Novorizontino</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Coritiba</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL17" s="3" t="n">
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL20" s="3" t="n">
         <v>45883.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2300,16 +2300,16 @@
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2432,16 +2432,16 @@
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL20"/>
+  <dimension ref="A1:AL17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -1070,40 +1070,40 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -1112,16 +1112,16 @@
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1130,10 +1130,10 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="M9" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="N9" t="n">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,40 +2126,40 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2186,10 +2186,10 @@
         <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH13" t="n">
         <v>0</v>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="AL14" s="3" t="n">
-        <v>45883.79166666666</v>
+        <v>45883.83333333334</v>
       </c>
     </row>
     <row r="15">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,40 +2390,40 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.35</v>
+        <v>4.1</v>
       </c>
       <c r="M15" t="n">
-        <v>4.2</v>
+        <v>2.85</v>
       </c>
       <c r="N15" t="n">
-        <v>7.1</v>
+        <v>1.9</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -2432,16 +2432,16 @@
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.37</v>
+        <v>2.28</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2450,10 +2450,10 @@
         <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH15" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="AL15" s="3" t="n">
-        <v>45883.79166666666</v>
+        <v>45883.89583333334</v>
       </c>
     </row>
     <row r="16">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,40 +2522,40 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2582,10 +2582,10 @@
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH16" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="AL16" s="3" t="n">
-        <v>45883.79166666666</v>
+        <v>45883.89583333334</v>
       </c>
     </row>
     <row r="17">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2736,402 +2736,6 @@
         </is>
       </c>
       <c r="AL17" s="3" t="n">
-        <v>45883.83333333334</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>45883</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>South America Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Universitario</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Palmeiras</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL18" s="3" t="n">
-        <v>45883.89583333334</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>45883</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>South America Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Libertad</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>River Plate</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="M19" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL19" s="3" t="n">
-        <v>45883.89583333334</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>45883</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>21:35</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Novorizontino</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Coritiba</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL20" s="3" t="n">
         <v>45883.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL17"/>
+  <dimension ref="A1:AL16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -638,22 +638,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -674,76 +674,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -765,12 +765,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="AL3" s="3" t="n">
-        <v>45883.45833333334</v>
+        <v>45883.5</v>
       </c>
     </row>
     <row r="4">
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,40 +938,40 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -980,16 +980,16 @@
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -998,10 +998,10 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,40 +1070,40 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -1112,16 +1112,16 @@
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1130,10 +1130,10 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>45883.5</v>
+        <v>45883.52083333334</v>
       </c>
     </row>
     <row r="7">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>45883.52083333334</v>
+        <v>45883.58333333334</v>
       </c>
     </row>
     <row r="8">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.92</v>
+        <v>2.1</v>
       </c>
       <c r="M8" t="n">
-        <v>2.65</v>
+        <v>3.63</v>
       </c>
       <c r="N8" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="O8" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.98</v>
+        <v>1.55</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.36</v>
+        <v>2.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>45883.58333333334</v>
+        <v>45883.60416666666</v>
       </c>
     </row>
     <row r="9">
@@ -1557,12 +1557,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>45883.60416666666</v>
+        <v>45883.61458333334</v>
       </c>
     </row>
     <row r="10">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>45883.61458333334</v>
+        <v>45883.625</v>
       </c>
     </row>
     <row r="11">
@@ -1821,27 +1821,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1865,73 +1865,73 @@
         <v>1.4</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="N11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O11" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="P11" t="n">
         <v>2.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>7.55</v>
+        <v>8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH11" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="AL11" s="3" t="n">
-        <v>45883.625</v>
+        <v>45883.79166666666</v>
       </c>
     </row>
     <row r="12">
@@ -2085,12 +2085,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,40 +2126,40 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2186,10 +2186,10 @@
         <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
         <v>0</v>
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="AL13" s="3" t="n">
-        <v>45883.79166666666</v>
+        <v>45883.83333333334</v>
       </c>
     </row>
     <row r="14">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,40 +2258,40 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2318,10 +2318,10 @@
         <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="AL14" s="3" t="n">
-        <v>45883.83333333334</v>
+        <v>45883.89583333334</v>
       </c>
     </row>
     <row r="15">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.91</v>
+        <v>2.21</v>
       </c>
       <c r="M16" t="n">
-        <v>3.21</v>
+        <v>2.57</v>
       </c>
       <c r="N16" t="n">
-        <v>1.81</v>
+        <v>3.6</v>
       </c>
       <c r="O16" t="n">
-        <v>4.75</v>
+        <v>3.2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="Q16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V16" t="n">
+        <v>15</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF16" t="n">
         <v>2.5</v>
       </c>
-      <c r="R16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V16" t="n">
-        <v>9</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AG16" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2604,138 +2604,6 @@
         </is>
       </c>
       <c r="AL16" s="3" t="n">
-        <v>45883.89583333334</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>45883</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>21:35</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Novorizontino</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Coritiba</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="M17" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="T17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V17" t="n">
-        <v>9</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL17" s="3" t="n">
         <v>45883.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.92</v>
+        <v>3.21</v>
       </c>
       <c r="M7" t="n">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="N7" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="O7" t="n">
         <v>4.67</v>
@@ -1376,10 +1376,10 @@
         <v>5.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="AB7" t="n">
         <v>2.98</v>
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="M8" t="n">
-        <v>3.63</v>
+        <v>3.75</v>
       </c>
       <c r="N8" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="M10" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="N10" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="O10" t="n">
         <v>1.92</v>
@@ -1778,10 +1778,10 @@
         <v>3.24</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AD10" t="n">
         <v>3.2</v>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -686,22 +686,22 @@
         <v>4</v>
       </c>
       <c r="P2" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="R2" t="n">
         <v>1.43</v>
       </c>
       <c r="S2" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="T2" t="n">
         <v>2.9</v>
       </c>
       <c r="U2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V2" t="n">
         <v>7.8</v>
@@ -716,7 +716,7 @@
         <v>7.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AA2" t="n">
         <v>2.88</v>
@@ -734,7 +734,7 @@
         <v>1.21</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG2" t="n">
         <v>1.83</v>
@@ -765,12 +765,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,40 +806,40 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -848,16 +848,16 @@
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
@@ -866,10 +866,10 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH3" t="n">
         <v>0</v>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="AL3" s="3" t="n">
-        <v>45883.5</v>
+        <v>45883.45833333334</v>
       </c>
     </row>
     <row r="4">
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,40 +938,40 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -980,16 +980,16 @@
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -998,10 +998,10 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
@@ -1334,19 +1334,19 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.21</v>
+        <v>3.92</v>
       </c>
       <c r="M7" t="n">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="N7" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="O7" t="n">
         <v>4.67</v>
       </c>
       <c r="P7" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="Q7" t="n">
         <v>3</v>
@@ -1355,13 +1355,13 @@
         <v>1.62</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="T7" t="n">
         <v>3.8</v>
       </c>
       <c r="U7" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="V7" t="n">
         <v>9.9</v>
@@ -1373,13 +1373,13 @@
         <v>1.12</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="AB7" t="n">
         <v>2.98</v>
@@ -1391,7 +1391,7 @@
         <v>5.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF7" t="n">
         <v>2.2</v>
@@ -1425,12 +1425,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="M8" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="N8" t="n">
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>8.31</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.3</v>
+        <v>1.79</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>45883.60416666666</v>
+        <v>45883.58333333334</v>
       </c>
     </row>
     <row r="9">
@@ -1557,12 +1557,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>45883.61458333334</v>
+        <v>45883.60416666666</v>
       </c>
     </row>
     <row r="10">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.55</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>45883.625</v>
+        <v>45883.61458333334</v>
       </c>
     </row>
     <row r="11">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,70 +2258,70 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.91</v>
+        <v>4.1</v>
       </c>
       <c r="M14" t="n">
-        <v>3.21</v>
+        <v>2.85</v>
       </c>
       <c r="N14" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="O14" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="P14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S14" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V14" t="n">
+        <v>15</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
         <v>2.5</v>
       </c>
-      <c r="R14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V14" t="n">
-        <v>9</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AG14" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,40 +2390,40 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="M15" t="n">
-        <v>2.85</v>
+        <v>3.21</v>
       </c>
       <c r="N15" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="O15" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="P15" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="T15" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="U15" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -2432,16 +2432,16 @@
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2450,10 +2450,10 @@
         <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AH15" t="n">
         <v>0</v>
@@ -2537,49 +2537,49 @@
         <v>1.72</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.7</v>
+        <v>4.01</v>
       </c>
       <c r="R16" t="n">
         <v>1.65</v>
       </c>
       <c r="S16" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="T16" t="n">
-        <v>4.33</v>
+        <v>3.95</v>
       </c>
       <c r="U16" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="V16" t="n">
         <v>15</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Z16" t="n">
         <v>1.63</v>
       </c>
       <c r="AA16" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AD16" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF16" t="n">
         <v>2.5</v>
@@ -2591,7 +2591,7 @@
         <v>10</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -683,13 +683,13 @@
         <v>2.05</v>
       </c>
       <c r="O2" t="n">
-        <v>4</v>
+        <v>2.45</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1</v>
+        <v>7</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.7</v>
+        <v>1.83</v>
       </c>
       <c r="R2" t="n">
         <v>1.43</v>
@@ -815,13 +815,13 @@
         <v>2.44</v>
       </c>
       <c r="O3" t="n">
-        <v>4.33</v>
+        <v>2.6</v>
       </c>
       <c r="P3" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.4</v>
+        <v>2.05</v>
       </c>
       <c r="R3" t="n">
         <v>1.8</v>
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.92</v>
+        <v>1.4</v>
       </c>
       <c r="M7" t="n">
-        <v>2.65</v>
+        <v>4</v>
       </c>
       <c r="N7" t="n">
-        <v>2.2</v>
+        <v>7</v>
       </c>
       <c r="O7" t="n">
-        <v>4.67</v>
+        <v>1.38</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7</v>
+        <v>8.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="R7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V7" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.62</v>
       </c>
-      <c r="S7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V7" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AH7" t="n">
-        <v>11.5</v>
+        <v>5.8</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.4</v>
+        <v>3.92</v>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
+        <v>2.65</v>
       </c>
       <c r="N8" t="n">
-        <v>7</v>
+        <v>2.2</v>
       </c>
       <c r="O8" t="n">
-        <v>1.92</v>
+        <v>2.55</v>
       </c>
       <c r="P8" t="n">
-        <v>2.38</v>
+        <v>5.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.31</v>
+        <v>1.95</v>
       </c>
       <c r="R8" t="n">
-        <v>1.37</v>
+        <v>1.62</v>
       </c>
       <c r="S8" t="n">
-        <v>2.76</v>
+        <v>2.05</v>
       </c>
       <c r="T8" t="n">
-        <v>2.85</v>
+        <v>3.8</v>
       </c>
       <c r="U8" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="V8" t="n">
-        <v>7.1</v>
+        <v>9.9</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.5</v>
+        <v>4.8</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.24</v>
+        <v>2.29</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>2.98</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.79</v>
+        <v>1.36</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AH8" t="n">
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1871,13 +1871,13 @@
         <v>9</v>
       </c>
       <c r="O11" t="n">
-        <v>1.91</v>
+        <v>1.36</v>
       </c>
       <c r="P11" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="R11" t="n">
         <v>1.36</v>
@@ -2267,13 +2267,13 @@
         <v>1.9</v>
       </c>
       <c r="O14" t="n">
-        <v>5.5</v>
+        <v>2.75</v>
       </c>
       <c r="P14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.75</v>
+        <v>1.73</v>
       </c>
       <c r="R14" t="n">
         <v>1.67</v>
@@ -2399,13 +2399,13 @@
         <v>1.81</v>
       </c>
       <c r="O15" t="n">
-        <v>4.75</v>
+        <v>2.6</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="R15" t="n">
         <v>1.44</v>
@@ -2531,13 +2531,13 @@
         <v>3.6</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2</v>
+        <v>1.95</v>
       </c>
       <c r="P16" t="n">
-        <v>1.72</v>
+        <v>5</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.01</v>
+        <v>2.62</v>
       </c>
       <c r="R16" t="n">
         <v>1.65</v>
@@ -2564,10 +2564,10 @@
         <v>5</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AB16" t="n">
         <v>3.1</v>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL16"/>
+  <dimension ref="A1:AL17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.4</v>
+        <v>3.92</v>
       </c>
       <c r="M7" t="n">
-        <v>4</v>
+        <v>2.65</v>
       </c>
       <c r="N7" t="n">
-        <v>7</v>
+        <v>2.2</v>
       </c>
       <c r="O7" t="n">
-        <v>1.38</v>
+        <v>2.55</v>
       </c>
       <c r="P7" t="n">
-        <v>8.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.9</v>
+        <v>1.95</v>
       </c>
       <c r="R7" t="n">
-        <v>1.37</v>
+        <v>1.62</v>
       </c>
       <c r="S7" t="n">
-        <v>2.76</v>
+        <v>2.05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.85</v>
+        <v>3.8</v>
       </c>
       <c r="U7" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="V7" t="n">
-        <v>7.1</v>
+        <v>9.9</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.5</v>
+        <v>4.8</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.24</v>
+        <v>2.29</v>
       </c>
       <c r="AB7" t="n">
-        <v>2</v>
+        <v>2.98</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.79</v>
+        <v>1.36</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AH7" t="n">
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.92</v>
+        <v>1.4</v>
       </c>
       <c r="M8" t="n">
-        <v>2.65</v>
+        <v>4</v>
       </c>
       <c r="N8" t="n">
-        <v>2.2</v>
+        <v>7</v>
       </c>
       <c r="O8" t="n">
-        <v>2.55</v>
+        <v>1.38</v>
       </c>
       <c r="P8" t="n">
-        <v>5.25</v>
+        <v>8.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.95</v>
+        <v>3.9</v>
       </c>
       <c r="R8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V8" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.62</v>
       </c>
-      <c r="S8" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V8" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AH8" t="n">
-        <v>11.5</v>
+        <v>5.8</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>2.06</v>
       </c>
       <c r="M12" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="N12" t="n">
-        <v>7.1</v>
+        <v>3.5</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>2.37</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.88</v>
+        <v>2.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.82</v>
+        <v>1.46</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2085,12 +2085,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2168,16 +2168,16 @@
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="AL13" s="3" t="n">
-        <v>45883.83333333334</v>
+        <v>45883.79166666666</v>
       </c>
     </row>
     <row r="14">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,40 +2258,40 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.1</v>
+        <v>1.35</v>
       </c>
       <c r="M14" t="n">
-        <v>2.85</v>
+        <v>4.2</v>
       </c>
       <c r="N14" t="n">
-        <v>1.9</v>
+        <v>7.1</v>
       </c>
       <c r="O14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -2300,16 +2300,16 @@
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.28</v>
+        <v>2.37</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2318,10 +2318,10 @@
         <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="AL14" s="3" t="n">
-        <v>45883.89583333334</v>
+        <v>45883.79166666666</v>
       </c>
     </row>
     <row r="15">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,34 +2522,34 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.21</v>
+        <v>4.1</v>
       </c>
       <c r="M16" t="n">
-        <v>2.57</v>
+        <v>2.85</v>
       </c>
       <c r="N16" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="O16" t="n">
-        <v>1.95</v>
+        <v>2.75</v>
       </c>
       <c r="P16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.62</v>
+        <v>1.73</v>
       </c>
       <c r="R16" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="S16" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="T16" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="V16" t="n">
         <v>15</v>
@@ -2558,52 +2558,184 @@
         <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AA16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB16" t="n">
         <v>2.15</v>
       </c>
-      <c r="AB16" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AC16" t="n">
-        <v>1.31</v>
+        <v>1.57</v>
       </c>
       <c r="AD16" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
         <v>2.5</v>
       </c>
       <c r="AG16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL16" s="3" t="n">
+        <v>45883.89583333334</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>45883</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P17" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V17" t="n">
+        <v>15</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.53</v>
       </c>
-      <c r="AH16" t="n">
+      <c r="AH17" t="n">
         <v>10</v>
       </c>
-      <c r="AI16" t="n">
+      <c r="AI17" t="n">
         <v>1.02</v>
       </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL16" s="3" t="n">
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL17" s="3" t="n">
         <v>45883.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -648,12 +648,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -674,76 +674,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="M2" t="n">
-        <v>3.05</v>
+        <v>2.42</v>
       </c>
       <c r="N2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
         <v>2.05</v>
       </c>
-      <c r="O2" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="P2" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.83</v>
-      </c>
       <c r="R2" t="n">
-        <v>1.43</v>
+        <v>1.8</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="T2" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="U2" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="V2" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="W2" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.1</v>
+        <v>3.75</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.83</v>
+        <v>1.4</v>
       </c>
       <c r="AH2" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="M3" t="n">
-        <v>2.42</v>
+        <v>3.05</v>
       </c>
       <c r="N3" t="n">
-        <v>2.44</v>
+        <v>2.05</v>
       </c>
       <c r="O3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P3" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S3" t="n">
         <v>2.6</v>
       </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.91</v>
-      </c>
       <c r="T3" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="V3" t="n">
-        <v>11</v>
+        <v>6.8</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.8</v>
+        <v>1.32</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.9</v>
+        <v>2.88</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.75</v>
+        <v>2.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.25</v>
+        <v>1.66</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -897,27 +897,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="AL4" s="3" t="n">
-        <v>45883.5</v>
+        <v>45883.45833333334</v>
       </c>
     </row>
     <row r="5">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>45883.52083333334</v>
+        <v>45883.5</v>
       </c>
     </row>
     <row r="7">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>45883.58333333334</v>
+        <v>45883.52083333334</v>
       </c>
     </row>
     <row r="8">
@@ -1469,10 +1469,10 @@
         <v>1.4</v>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
+        <v>4.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="O8" t="n">
         <v>1.38</v>
@@ -1487,7 +1487,7 @@
         <v>1.37</v>
       </c>
       <c r="S8" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="T8" t="n">
         <v>2.85</v>
@@ -1508,25 +1508,25 @@
         <v>8.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AE8" t="n">
         <v>1.29</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AG8" t="n">
         <v>1.62</v>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P9" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Q9" t="n">
         <v>1.95</v>
       </c>
-      <c r="M9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.55</v>
+        <v>2.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.3</v>
+        <v>1.35</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>45883.60416666666</v>
+        <v>45883.58333333334</v>
       </c>
     </row>
     <row r="10">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>45883.61458333334</v>
+        <v>45883.60416666666</v>
       </c>
     </row>
     <row r="11">
@@ -1821,27 +1821,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,40 +1862,40 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1922,10 +1922,10 @@
         <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
         <v>0</v>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="AL11" s="3" t="n">
-        <v>45883.79166666666</v>
+        <v>45883.61458333334</v>
       </c>
     </row>
     <row r="12">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,40 +1994,40 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.06</v>
+        <v>1.4</v>
       </c>
       <c r="M12" t="n">
-        <v>3.05</v>
+        <v>4.33</v>
       </c>
       <c r="N12" t="n">
+        <v>9</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>3.5</v>
       </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.46</v>
+        <v>1.85</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2054,10 +2054,10 @@
         <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH12" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.23</v>
+        <v>1.35</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="N13" t="n">
-        <v>3.25</v>
+        <v>7.1</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2168,16 +2168,16 @@
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.87</v>
+        <v>1.88</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.4</v>
+        <v>1.82</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2300,16 +2300,16 @@
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="AL14" s="3" t="n">
-        <v>45883.79166666666</v>
+        <v>45883.83333333334</v>
       </c>
     </row>
     <row r="15">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,40 +2390,40 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.91</v>
+        <v>4.1</v>
       </c>
       <c r="M15" t="n">
-        <v>3.21</v>
+        <v>2.85</v>
       </c>
       <c r="N15" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="O15" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R15" t="n">
         <v>1.67</v>
       </c>
-      <c r="R15" t="n">
-        <v>1.44</v>
-      </c>
       <c r="S15" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="T15" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="V15" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -2432,16 +2432,16 @@
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2450,10 +2450,10 @@
         <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AH15" t="n">
         <v>0</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,40 +2522,40 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="M16" t="n">
-        <v>2.85</v>
+        <v>3.21</v>
       </c>
       <c r="N16" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="O16" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="R16" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="U16" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -2564,16 +2564,16 @@
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2582,10 +2582,10 @@
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AH16" t="n">
         <v>0</v>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL17"/>
+  <dimension ref="A1:AL16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -648,12 +648,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -674,76 +674,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="M2" t="n">
-        <v>2.42</v>
+        <v>3.05</v>
       </c>
       <c r="N2" t="n">
-        <v>2.44</v>
+        <v>2.05</v>
       </c>
       <c r="O2" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S2" t="n">
         <v>2.6</v>
       </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.91</v>
-      </c>
       <c r="T2" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="V2" t="n">
-        <v>11</v>
+        <v>6.8</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.8</v>
+        <v>1.32</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.9</v>
+        <v>2.88</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.75</v>
+        <v>2.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.25</v>
+        <v>1.66</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="M3" t="n">
-        <v>3.05</v>
+        <v>2.42</v>
       </c>
       <c r="N3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>2.05</v>
       </c>
-      <c r="O3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="P3" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.83</v>
-      </c>
       <c r="R3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V3" t="n">
+        <v>11</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG3" t="n">
         <v>1.4</v>
       </c>
-      <c r="S3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AH3" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -897,27 +897,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="AL4" s="3" t="n">
-        <v>45883.45833333334</v>
+        <v>45883.5</v>
       </c>
     </row>
     <row r="5">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>45883.5</v>
+        <v>45883.52083333334</v>
       </c>
     </row>
     <row r="7">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>45883.52083333334</v>
+        <v>45883.58333333334</v>
       </c>
     </row>
     <row r="8">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="M8" t="n">
-        <v>4.16</v>
+        <v>3.89</v>
       </c>
       <c r="N8" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="O8" t="n">
         <v>1.38</v>
@@ -1514,10 +1514,10 @@
         <v>3.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AD8" t="n">
         <v>3.5</v>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.92</v>
+        <v>1.95</v>
       </c>
       <c r="M9" t="n">
-        <v>2.65</v>
+        <v>3.75</v>
       </c>
       <c r="N9" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="O9" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.7</v>
+        <v>1.55</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.35</v>
+        <v>2.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>45883.58333333334</v>
+        <v>45883.60416666666</v>
       </c>
     </row>
     <row r="10">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>45883.60416666666</v>
+        <v>45883.61458333334</v>
       </c>
     </row>
     <row r="11">
@@ -1821,27 +1821,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,40 +1862,40 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1922,10 +1922,10 @@
         <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH11" t="n">
         <v>0</v>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="AL11" s="3" t="n">
-        <v>45883.61458333334</v>
+        <v>45883.79166666666</v>
       </c>
     </row>
     <row r="12">
@@ -1994,40 +1994,40 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="N12" t="n">
-        <v>9</v>
+        <v>7.1</v>
       </c>
       <c r="O12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2054,10 +2054,10 @@
         <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
         <v>0</v>
@@ -2085,12 +2085,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2168,16 +2168,16 @@
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="AL13" s="3" t="n">
-        <v>45883.79166666666</v>
+        <v>45883.83333333334</v>
       </c>
     </row>
     <row r="14">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,40 +2258,40 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2318,10 +2318,10 @@
         <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="AL14" s="3" t="n">
-        <v>45883.83333333334</v>
+        <v>45883.89583333334</v>
       </c>
     </row>
     <row r="15">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.91</v>
+        <v>2.21</v>
       </c>
       <c r="M16" t="n">
-        <v>3.21</v>
+        <v>2.57</v>
       </c>
       <c r="N16" t="n">
-        <v>1.81</v>
+        <v>3.6</v>
       </c>
       <c r="O16" t="n">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.67</v>
       </c>
-      <c r="R16" t="n">
-        <v>1.44</v>
-      </c>
       <c r="S16" t="n">
-        <v>2.63</v>
+        <v>2.11</v>
       </c>
       <c r="T16" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="V16" t="n">
         <v>9</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.12</v>
+        <v>3.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.72</v>
+        <v>1.27</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2604,138 +2604,6 @@
         </is>
       </c>
       <c r="AL16" s="3" t="n">
-        <v>45883.89583333334</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>45883</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>21:35</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Novorizontino</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Coritiba</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="M17" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="P17" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V17" t="n">
-        <v>15</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL17" s="3" t="n">
         <v>45883.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -648,12 +648,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -674,76 +674,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="M2" t="n">
-        <v>3.05</v>
+        <v>2.42</v>
       </c>
       <c r="N2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
         <v>2.05</v>
       </c>
-      <c r="O2" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="P2" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.83</v>
-      </c>
       <c r="R2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V2" t="n">
+        <v>11</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG2" t="n">
         <v>1.4</v>
       </c>
-      <c r="S2" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AH2" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="M3" t="n">
-        <v>2.42</v>
+        <v>3.05</v>
       </c>
       <c r="N3" t="n">
-        <v>2.44</v>
+        <v>2.05</v>
       </c>
       <c r="O3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P3" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S3" t="n">
         <v>2.6</v>
       </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.91</v>
-      </c>
       <c r="T3" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="V3" t="n">
-        <v>11</v>
+        <v>6.8</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.8</v>
+        <v>1.32</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.9</v>
+        <v>2.88</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.75</v>
+        <v>2.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.25</v>
+        <v>1.66</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.21</v>
+        <v>1.37</v>
       </c>
       <c r="M7" t="n">
-        <v>2.58</v>
+        <v>3.89</v>
       </c>
       <c r="N7" t="n">
-        <v>2.38</v>
+        <v>7.4</v>
       </c>
       <c r="O7" t="n">
-        <v>2.55</v>
+        <v>1.38</v>
       </c>
       <c r="P7" t="n">
-        <v>5.25</v>
+        <v>8.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.95</v>
+        <v>3.9</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="S7" t="n">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="T7" t="n">
-        <v>3.7</v>
+        <v>2.85</v>
       </c>
       <c r="U7" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="V7" t="n">
-        <v>9.9</v>
+        <v>7.1</v>
       </c>
       <c r="W7" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.7</v>
+        <v>8.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.7</v>
+        <v>1.96</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.35</v>
+        <v>1.74</v>
       </c>
       <c r="AD7" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH7" t="n">
-        <v>11.5</v>
+        <v>5.8</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.37</v>
+        <v>3.21</v>
       </c>
       <c r="M8" t="n">
-        <v>3.89</v>
+        <v>2.58</v>
       </c>
       <c r="N8" t="n">
-        <v>7.4</v>
+        <v>2.38</v>
       </c>
       <c r="O8" t="n">
-        <v>1.38</v>
+        <v>2.55</v>
       </c>
       <c r="P8" t="n">
-        <v>8.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.9</v>
+        <v>1.95</v>
       </c>
       <c r="R8" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="S8" t="n">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="T8" t="n">
-        <v>2.85</v>
+        <v>3.7</v>
       </c>
       <c r="U8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V8" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC8" t="n">
         <v>1.35</v>
       </c>
-      <c r="V8" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AD8" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH8" t="n">
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1862,40 +1862,40 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M11" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="N11" t="n">
-        <v>9</v>
+        <v>7.1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1904,16 +1904,16 @@
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1922,10 +1922,10 @@
         <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
         <v>0</v>
@@ -1994,40 +1994,40 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M12" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="N12" t="n">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2054,10 +2054,10 @@
         <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH12" t="n">
         <v>0</v>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -648,12 +648,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -674,76 +674,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="M2" t="n">
-        <v>2.42</v>
+        <v>3.05</v>
       </c>
       <c r="N2" t="n">
-        <v>2.44</v>
+        <v>2.05</v>
       </c>
       <c r="O2" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S2" t="n">
         <v>2.6</v>
       </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.91</v>
-      </c>
       <c r="T2" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="V2" t="n">
-        <v>11</v>
+        <v>6.8</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.8</v>
+        <v>1.32</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.9</v>
+        <v>2.88</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.75</v>
+        <v>2.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.25</v>
+        <v>1.66</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="M3" t="n">
-        <v>3.05</v>
+        <v>2.42</v>
       </c>
       <c r="N3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>2.05</v>
       </c>
-      <c r="O3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="P3" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.83</v>
-      </c>
       <c r="R3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V3" t="n">
+        <v>11</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG3" t="n">
         <v>1.4</v>
       </c>
-      <c r="S3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AH3" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.37</v>
+        <v>3.21</v>
       </c>
       <c r="M7" t="n">
-        <v>3.89</v>
+        <v>2.58</v>
       </c>
       <c r="N7" t="n">
-        <v>7.4</v>
+        <v>2.38</v>
       </c>
       <c r="O7" t="n">
-        <v>1.38</v>
+        <v>2.55</v>
       </c>
       <c r="P7" t="n">
-        <v>8.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.9</v>
+        <v>1.95</v>
       </c>
       <c r="R7" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="S7" t="n">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="T7" t="n">
-        <v>2.85</v>
+        <v>3.7</v>
       </c>
       <c r="U7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V7" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC7" t="n">
         <v>1.35</v>
       </c>
-      <c r="V7" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AD7" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH7" t="n">
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.21</v>
+        <v>1.37</v>
       </c>
       <c r="M8" t="n">
-        <v>2.58</v>
+        <v>3.89</v>
       </c>
       <c r="N8" t="n">
-        <v>2.38</v>
+        <v>7.4</v>
       </c>
       <c r="O8" t="n">
-        <v>2.55</v>
+        <v>1.38</v>
       </c>
       <c r="P8" t="n">
-        <v>5.25</v>
+        <v>8.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.95</v>
+        <v>3.9</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="S8" t="n">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="T8" t="n">
-        <v>3.7</v>
+        <v>2.85</v>
       </c>
       <c r="U8" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="V8" t="n">
-        <v>9.9</v>
+        <v>7.1</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.7</v>
+        <v>8.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.7</v>
+        <v>1.96</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.35</v>
+        <v>1.74</v>
       </c>
       <c r="AD8" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH8" t="n">
-        <v>11.5</v>
+        <v>5.8</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -648,12 +648,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -674,76 +674,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="M2" t="n">
-        <v>3.05</v>
+        <v>2.42</v>
       </c>
       <c r="N2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
         <v>2.05</v>
       </c>
-      <c r="O2" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="P2" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.83</v>
-      </c>
       <c r="R2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V2" t="n">
+        <v>11</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG2" t="n">
         <v>1.4</v>
       </c>
-      <c r="S2" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AH2" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="M3" t="n">
-        <v>2.42</v>
+        <v>3.05</v>
       </c>
       <c r="N3" t="n">
-        <v>2.44</v>
+        <v>2.05</v>
       </c>
       <c r="O3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P3" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S3" t="n">
         <v>2.6</v>
       </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.91</v>
-      </c>
       <c r="T3" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="V3" t="n">
-        <v>11</v>
+        <v>6.8</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.8</v>
+        <v>1.32</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.9</v>
+        <v>2.88</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.75</v>
+        <v>2.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.25</v>
+        <v>1.66</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.21</v>
+        <v>1.37</v>
       </c>
       <c r="M7" t="n">
-        <v>2.58</v>
+        <v>3.89</v>
       </c>
       <c r="N7" t="n">
-        <v>2.38</v>
+        <v>7.4</v>
       </c>
       <c r="O7" t="n">
-        <v>2.55</v>
+        <v>1.38</v>
       </c>
       <c r="P7" t="n">
-        <v>5.25</v>
+        <v>8.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.95</v>
+        <v>3.9</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="S7" t="n">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="T7" t="n">
-        <v>3.7</v>
+        <v>2.85</v>
       </c>
       <c r="U7" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="V7" t="n">
-        <v>9.9</v>
+        <v>7.1</v>
       </c>
       <c r="W7" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.7</v>
+        <v>8.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.7</v>
+        <v>1.96</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.35</v>
+        <v>1.74</v>
       </c>
       <c r="AD7" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH7" t="n">
-        <v>11.5</v>
+        <v>5.8</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.37</v>
+        <v>3.21</v>
       </c>
       <c r="M8" t="n">
-        <v>3.89</v>
+        <v>2.58</v>
       </c>
       <c r="N8" t="n">
-        <v>7.4</v>
+        <v>2.38</v>
       </c>
       <c r="O8" t="n">
-        <v>1.38</v>
+        <v>2.55</v>
       </c>
       <c r="P8" t="n">
-        <v>8.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.9</v>
+        <v>1.95</v>
       </c>
       <c r="R8" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="S8" t="n">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="T8" t="n">
-        <v>2.85</v>
+        <v>3.7</v>
       </c>
       <c r="U8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V8" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC8" t="n">
         <v>1.35</v>
       </c>
-      <c r="V8" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AD8" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH8" t="n">
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="N11" t="n">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.37</v>
+        <v>3.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1994,40 +1994,40 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="N12" t="n">
-        <v>9</v>
+        <v>7.1</v>
       </c>
       <c r="O12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2054,10 +2054,10 @@
         <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
         <v>0</v>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.91</v>
+        <v>4.1</v>
       </c>
       <c r="M14" t="n">
-        <v>3.21</v>
+        <v>2.85</v>
       </c>
       <c r="N14" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="O14" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R14" t="n">
         <v>1.67</v>
       </c>
-      <c r="R14" t="n">
-        <v>1.44</v>
-      </c>
       <c r="S14" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="T14" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="V14" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="M15" t="n">
-        <v>2.85</v>
+        <v>3.21</v>
       </c>
       <c r="N15" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="O15" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="R15" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="T15" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="U15" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.63</v>
+        <v>1.42</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.28</v>
+        <v>2.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -648,12 +648,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -674,76 +674,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.37</v>
+        <v>3.49</v>
       </c>
       <c r="M2" t="n">
-        <v>2.42</v>
+        <v>3.05</v>
       </c>
       <c r="N2" t="n">
-        <v>2.44</v>
+        <v>2.09</v>
       </c>
       <c r="O2" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="S2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG2" t="n">
         <v>1.91</v>
       </c>
-      <c r="T2" t="n">
-        <v>5</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="V2" t="n">
-        <v>11</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="M3" t="n">
-        <v>3.05</v>
+        <v>2.42</v>
       </c>
       <c r="N3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>2.05</v>
       </c>
-      <c r="O3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="P3" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.83</v>
-      </c>
       <c r="R3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V3" t="n">
+        <v>11</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG3" t="n">
         <v>1.4</v>
       </c>
-      <c r="S3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AH3" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1256,10 +1256,10 @@
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.37</v>
+        <v>3.35</v>
       </c>
       <c r="M7" t="n">
-        <v>3.89</v>
+        <v>2.65</v>
       </c>
       <c r="N7" t="n">
-        <v>7.4</v>
+        <v>2.45</v>
       </c>
       <c r="O7" t="n">
-        <v>1.38</v>
+        <v>2.55</v>
       </c>
       <c r="P7" t="n">
-        <v>8.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.9</v>
+        <v>1.95</v>
       </c>
       <c r="R7" t="n">
-        <v>1.37</v>
+        <v>1.74</v>
       </c>
       <c r="S7" t="n">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="T7" t="n">
-        <v>2.85</v>
+        <v>3.8</v>
       </c>
       <c r="U7" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="V7" t="n">
-        <v>7.1</v>
+        <v>12</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.5</v>
+        <v>5.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.27</v>
+        <v>1.58</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.96</v>
+        <v>2.88</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.74</v>
+        <v>1.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH7" t="n">
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.21</v>
+        <v>1.37</v>
       </c>
       <c r="M8" t="n">
-        <v>2.58</v>
+        <v>3.89</v>
       </c>
       <c r="N8" t="n">
-        <v>2.38</v>
+        <v>7.4</v>
       </c>
       <c r="O8" t="n">
-        <v>2.55</v>
+        <v>1.38</v>
       </c>
       <c r="P8" t="n">
-        <v>5.25</v>
+        <v>8.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.95</v>
+        <v>3.9</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>2.15</v>
+        <v>2.85</v>
       </c>
       <c r="T8" t="n">
-        <v>3.7</v>
+        <v>2.89</v>
       </c>
       <c r="U8" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="V8" t="n">
-        <v>9.9</v>
+        <v>6</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.7</v>
+        <v>9</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.7</v>
+        <v>1.96</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.35</v>
+        <v>1.74</v>
       </c>
       <c r="AD8" t="n">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH8" t="n">
-        <v>11.5</v>
+        <v>6.55</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -2306,10 +2306,10 @@
         <v>2.28</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.15</v>
+        <v>2.58</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AD14" t="n">
         <v>6.25</v>
@@ -2540,28 +2540,28 @@
         <v>2.62</v>
       </c>
       <c r="R16" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="S16" t="n">
         <v>2.11</v>
       </c>
       <c r="T16" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="U16" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="V16" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.79</v>
+        <v>5</v>
       </c>
       <c r="Z16" t="n">
         <v>1.62</v>
@@ -2570,28 +2570,28 @@
         <v>2.15</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AD16" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AH16" t="n">
         <v>10</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -695,7 +695,7 @@
         <v>1.47</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="T2" t="n">
         <v>3.18</v>
@@ -737,7 +737,7 @@
         <v>1.83</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH2" t="n">
         <v>7.2</v>
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,40 +1202,40 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="M6" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="N6" t="n">
-        <v>7.9</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD6" t="n">
         <v>2</v>
@@ -1262,10 +1262,10 @@
         <v>1.72</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.35</v>
+        <v>1.36</v>
       </c>
       <c r="M7" t="n">
-        <v>2.65</v>
+        <v>4.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.45</v>
+        <v>7.25</v>
       </c>
       <c r="O7" t="n">
-        <v>2.55</v>
+        <v>1.38</v>
       </c>
       <c r="P7" t="n">
-        <v>5.25</v>
+        <v>8.5</v>
       </c>
       <c r="Q7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V7" t="n">
+        <v>6</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB7" t="n">
         <v>1.95</v>
       </c>
-      <c r="R7" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V7" t="n">
-        <v>12</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.88</v>
-      </c>
       <c r="AC7" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>5.2</v>
+        <v>3.1</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH7" t="n">
-        <v>11.5</v>
+        <v>6.55</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.37</v>
+        <v>3.6</v>
       </c>
       <c r="M8" t="n">
-        <v>3.89</v>
+        <v>2.7</v>
       </c>
       <c r="N8" t="n">
-        <v>7.4</v>
+        <v>2.25</v>
       </c>
       <c r="O8" t="n">
-        <v>1.38</v>
+        <v>2.55</v>
       </c>
       <c r="P8" t="n">
-        <v>8.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.9</v>
+        <v>1.95</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.74</v>
       </c>
       <c r="S8" t="n">
-        <v>2.85</v>
+        <v>2.02</v>
       </c>
       <c r="T8" t="n">
-        <v>2.89</v>
+        <v>3.8</v>
       </c>
       <c r="U8" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="V8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="Y8" t="n">
-        <v>9</v>
+        <v>5.16</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.96</v>
+        <v>2.88</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.74</v>
+        <v>1.35</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.1</v>
+        <v>5.2</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AH8" t="n">
-        <v>6.55</v>
+        <v>11.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1598,40 +1598,40 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.95</v>
+        <v>2.24</v>
       </c>
       <c r="M9" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N9" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1646,7 +1646,7 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AC9" t="n">
         <v>2.3</v>
@@ -1658,10 +1658,10 @@
         <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH9" t="n">
         <v>0</v>
@@ -2552,34 +2552,34 @@
         <v>1.17</v>
       </c>
       <c r="V16" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W16" t="n">
         <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Y16" t="n">
         <v>5</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AB16" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AD16" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF16" t="n">
         <v>2.5</v>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -648,12 +648,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -674,76 +674,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.49</v>
+        <v>3.37</v>
       </c>
       <c r="M2" t="n">
-        <v>3.05</v>
+        <v>2.42</v>
       </c>
       <c r="N2" t="n">
-        <v>2.09</v>
+        <v>2.44</v>
       </c>
       <c r="O2" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="P2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.47</v>
+        <v>1.8</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="T2" t="n">
-        <v>3.18</v>
+        <v>5</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="V2" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="W2" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.11</v>
+        <v>1.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.1</v>
+        <v>3.75</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AH2" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.37</v>
+        <v>3.49</v>
       </c>
       <c r="M3" t="n">
-        <v>2.42</v>
+        <v>3.05</v>
       </c>
       <c r="N3" t="n">
-        <v>2.44</v>
+        <v>2.09</v>
       </c>
       <c r="O3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P3" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S3" t="n">
         <v>2.6</v>
       </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.91</v>
-      </c>
       <c r="T3" t="n">
-        <v>5</v>
+        <v>3.18</v>
       </c>
       <c r="U3" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="V3" t="n">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.9</v>
+        <v>3.11</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.75</v>
+        <v>2.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.36</v>
+        <v>3.35</v>
       </c>
       <c r="M7" t="n">
-        <v>4.1</v>
+        <v>2.65</v>
       </c>
       <c r="N7" t="n">
-        <v>7.25</v>
+        <v>2.45</v>
       </c>
       <c r="O7" t="n">
-        <v>1.38</v>
+        <v>2.55</v>
       </c>
       <c r="P7" t="n">
-        <v>8.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.9</v>
+        <v>1.95</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>1.74</v>
       </c>
       <c r="S7" t="n">
-        <v>2.85</v>
+        <v>2.02</v>
       </c>
       <c r="T7" t="n">
-        <v>2.89</v>
+        <v>3.8</v>
       </c>
       <c r="U7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V7" t="n">
+        <v>12</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AC7" t="n">
         <v>1.35</v>
       </c>
-      <c r="V7" t="n">
-        <v>6</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AD7" t="n">
-        <v>3.1</v>
+        <v>5.2</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AH7" t="n">
-        <v>6.55</v>
+        <v>11.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.6</v>
+        <v>1.37</v>
       </c>
       <c r="M8" t="n">
-        <v>2.7</v>
+        <v>3.89</v>
       </c>
       <c r="N8" t="n">
-        <v>2.25</v>
+        <v>7.4</v>
       </c>
       <c r="O8" t="n">
-        <v>2.55</v>
+        <v>1.38</v>
       </c>
       <c r="P8" t="n">
-        <v>5.25</v>
+        <v>8.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.95</v>
+        <v>3.9</v>
       </c>
       <c r="R8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AC8" t="n">
         <v>1.74</v>
       </c>
-      <c r="S8" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V8" t="n">
-        <v>12</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AD8" t="n">
-        <v>5.2</v>
+        <v>3.1</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AH8" t="n">
-        <v>11.5</v>
+        <v>6.55</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M11" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="N11" t="n">
-        <v>9</v>
+        <v>7.1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.4</v>
+        <v>2.37</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M12" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="N12" t="n">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.37</v>
+        <v>3.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="M6" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>7.9</v>
       </c>
       <c r="O6" t="n">
         <v>1.4</v>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.24</v>
+        <v>1.95</v>
       </c>
       <c r="M9" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N9" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="O9" t="n">
         <v>1.8</v>
@@ -1646,7 +1646,7 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AC9" t="n">
         <v>2.3</v>
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="N11" t="n">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.37</v>
+        <v>3.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="N12" t="n">
-        <v>9</v>
+        <v>7.1</v>
       </c>
       <c r="O12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.4</v>
+        <v>2.37</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="M14" t="n">
-        <v>2.85</v>
+        <v>3.21</v>
       </c>
       <c r="N14" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="O14" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="P14" t="n">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="R14" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="T14" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="U14" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.63</v>
+        <v>1.42</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.28</v>
+        <v>2.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.58</v>
+        <v>2.12</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="AD14" t="n">
-        <v>6.25</v>
+        <v>4.33</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AH14" t="n">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.91</v>
+        <v>4.1</v>
       </c>
       <c r="M15" t="n">
-        <v>3.21</v>
+        <v>2.85</v>
       </c>
       <c r="N15" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="O15" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="P15" t="n">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R15" t="n">
         <v>1.67</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V15" t="n">
+        <v>15</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AC15" t="n">
         <v>1.44</v>
       </c>
-      <c r="S15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V15" t="n">
-        <v>9</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AD15" t="n">
-        <v>4.33</v>
+        <v>6.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.91</v>
+        <v>4.1</v>
       </c>
       <c r="M14" t="n">
-        <v>3.21</v>
+        <v>2.85</v>
       </c>
       <c r="N14" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="O14" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="P14" t="n">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R14" t="n">
         <v>1.67</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V14" t="n">
+        <v>15</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AC14" t="n">
         <v>1.44</v>
       </c>
-      <c r="S14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V14" t="n">
-        <v>9</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AD14" t="n">
-        <v>4.33</v>
+        <v>6.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="M15" t="n">
-        <v>2.85</v>
+        <v>3.21</v>
       </c>
       <c r="N15" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="O15" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="P15" t="n">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="R15" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="T15" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="U15" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.63</v>
+        <v>1.42</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.28</v>
+        <v>2.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.58</v>
+        <v>2.12</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="AD15" t="n">
-        <v>6.25</v>
+        <v>4.33</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AH15" t="n">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2543,19 +2543,19 @@
         <v>1.68</v>
       </c>
       <c r="S16" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="U16" t="n">
         <v>1.17</v>
       </c>
       <c r="V16" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
         <v>1.15</v>
@@ -2567,10 +2567,10 @@
         <v>1.73</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AC16" t="n">
         <v>1.27</v>
@@ -2585,13 +2585,13 @@
         <v>2.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AH16" t="n">
         <v>10</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -806,13 +806,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="M3" t="n">
-        <v>3.05</v>
+        <v>3.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="O3" t="n">
         <v>2.45</v>
@@ -827,19 +827,19 @@
         <v>1.47</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="T3" t="n">
-        <v>3.18</v>
+        <v>3.05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="V3" t="n">
         <v>7.8</v>
       </c>
       <c r="W3" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X3" t="n">
         <v>1.03</v>
@@ -851,13 +851,13 @@
         <v>1.36</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.11</v>
+        <v>3.3</v>
       </c>
       <c r="AB3" t="n">
         <v>2.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AD3" t="n">
         <v>3.7</v>
@@ -866,16 +866,16 @@
         <v>1.22</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH3" t="n">
         <v>7.2</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.35</v>
+        <v>1.36</v>
       </c>
       <c r="M7" t="n">
-        <v>2.65</v>
+        <v>4.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.45</v>
+        <v>7.25</v>
       </c>
       <c r="O7" t="n">
-        <v>2.55</v>
+        <v>1.38</v>
       </c>
       <c r="P7" t="n">
-        <v>5.25</v>
+        <v>8.5</v>
       </c>
       <c r="Q7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V7" t="n">
+        <v>6</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB7" t="n">
         <v>1.95</v>
       </c>
-      <c r="R7" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V7" t="n">
-        <v>12</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.88</v>
-      </c>
       <c r="AC7" t="n">
-        <v>1.35</v>
+        <v>1.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>5.2</v>
+        <v>3.1</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AH7" t="n">
-        <v>11.5</v>
+        <v>6.55</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.37</v>
+        <v>3.6</v>
       </c>
       <c r="M8" t="n">
-        <v>3.89</v>
+        <v>2.6</v>
       </c>
       <c r="N8" t="n">
-        <v>7.4</v>
+        <v>2.25</v>
       </c>
       <c r="O8" t="n">
-        <v>1.38</v>
+        <v>2.55</v>
       </c>
       <c r="P8" t="n">
-        <v>8.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.9</v>
+        <v>1.95</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.74</v>
       </c>
       <c r="S8" t="n">
-        <v>2.85</v>
+        <v>2.15</v>
       </c>
       <c r="T8" t="n">
-        <v>2.89</v>
+        <v>3.8</v>
       </c>
       <c r="U8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V8" t="n">
+        <v>12</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AC8" t="n">
         <v>1.35</v>
       </c>
-      <c r="V8" t="n">
-        <v>6</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AD8" t="n">
-        <v>3.1</v>
+        <v>5.2</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH8" t="n">
-        <v>6.55</v>
+        <v>11.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M11" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="N11" t="n">
-        <v>9</v>
+        <v>7.1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.4</v>
+        <v>2.37</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M12" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="N12" t="n">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.37</v>
+        <v>3.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="M14" t="n">
-        <v>2.85</v>
+        <v>3.21</v>
       </c>
       <c r="N14" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="O14" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="P14" t="n">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="R14" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="T14" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="U14" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.63</v>
+        <v>1.42</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.28</v>
+        <v>2.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.58</v>
+        <v>2.12</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="AD14" t="n">
-        <v>6.25</v>
+        <v>4.33</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AH14" t="n">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.91</v>
+        <v>4.1</v>
       </c>
       <c r="M15" t="n">
-        <v>3.21</v>
+        <v>2.85</v>
       </c>
       <c r="N15" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="O15" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="P15" t="n">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R15" t="n">
         <v>1.67</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V15" t="n">
+        <v>15</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AC15" t="n">
         <v>1.44</v>
       </c>
-      <c r="S15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V15" t="n">
-        <v>9</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AD15" t="n">
-        <v>4.33</v>
+        <v>6.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2564,16 +2564,16 @@
         <v>5</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AD16" t="n">
         <v>7</v>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -722,10 +722,10 @@
         <v>1.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.75</v>
+        <v>3.41</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
@@ -806,13 +806,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.47</v>
+        <v>3.55</v>
       </c>
       <c r="M3" t="n">
         <v>3.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O3" t="n">
         <v>2.45</v>
@@ -824,40 +824,40 @@
         <v>1.83</v>
       </c>
       <c r="R3" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="S3" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T3" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="U3" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="V3" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.4</v>
+        <v>7.9</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AD3" t="n">
         <v>3.7</v>
@@ -866,13 +866,13 @@
         <v>1.22</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AH3" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="AI3" t="n">
         <v>1.05</v>
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AD6" t="n">
         <v>2</v>
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M7" t="n">
-        <v>4.1</v>
+        <v>3.89</v>
       </c>
       <c r="N7" t="n">
-        <v>7.25</v>
+        <v>7.4</v>
       </c>
       <c r="O7" t="n">
         <v>1.38</v>
@@ -1352,19 +1352,19 @@
         <v>3.9</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="S7" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="T7" t="n">
         <v>2.89</v>
       </c>
       <c r="U7" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="V7" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="W7" t="n">
         <v>1.08</v>
@@ -1379,25 +1379,25 @@
         <v>1.28</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AH7" t="n">
         <v>6.55</v>
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="M8" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="N8" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="O8" t="n">
         <v>2.55</v>
@@ -1484,7 +1484,7 @@
         <v>1.95</v>
       </c>
       <c r="R8" t="n">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="S8" t="n">
         <v>2.15</v>
@@ -1493,7 +1493,7 @@
         <v>3.8</v>
       </c>
       <c r="U8" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="V8" t="n">
         <v>12</v>
@@ -1505,31 +1505,31 @@
         <v>1.15</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.16</v>
+        <v>5.7</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AA8" t="n">
         <v>2.25</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AD8" t="n">
         <v>5.2</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AH8" t="n">
         <v>11.5</v>
@@ -1652,10 +1652,10 @@
         <v>2.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF9" t="n">
         <v>1.53</v>
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.91</v>
+        <v>4.1</v>
       </c>
       <c r="M14" t="n">
-        <v>3.21</v>
+        <v>2.85</v>
       </c>
       <c r="N14" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="O14" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="P14" t="n">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R14" t="n">
         <v>1.67</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V14" t="n">
+        <v>15</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AC14" t="n">
         <v>1.44</v>
       </c>
-      <c r="S14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V14" t="n">
-        <v>9</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AD14" t="n">
-        <v>4.33</v>
+        <v>6.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="M15" t="n">
-        <v>2.85</v>
+        <v>3.21</v>
       </c>
       <c r="N15" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="O15" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="P15" t="n">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="R15" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="T15" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="U15" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.63</v>
+        <v>1.42</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.28</v>
+        <v>2.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.58</v>
+        <v>2.12</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="AD15" t="n">
-        <v>6.25</v>
+        <v>4.33</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AH15" t="n">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2540,25 +2540,25 @@
         <v>2.62</v>
       </c>
       <c r="R16" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="U16" t="n">
         <v>1.17</v>
       </c>
       <c r="V16" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Y16" t="n">
         <v>5</v>
@@ -2576,22 +2576,22 @@
         <v>1.33</v>
       </c>
       <c r="AD16" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF16" t="n">
         <v>2.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AH16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -648,12 +648,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -674,76 +674,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.37</v>
+        <v>3.55</v>
       </c>
       <c r="M2" t="n">
-        <v>2.42</v>
+        <v>3.11</v>
       </c>
       <c r="N2" t="n">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="O2" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB2" t="n">
         <v>2.05</v>
       </c>
-      <c r="R2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="T2" t="n">
-        <v>5</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="V2" t="n">
-        <v>11</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>3.41</v>
-      </c>
       <c r="AC2" t="n">
-        <v>1.27</v>
+        <v>1.66</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.4</v>
+        <v>1.98</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.55</v>
+        <v>3.37</v>
       </c>
       <c r="M3" t="n">
-        <v>3.11</v>
+        <v>2.42</v>
       </c>
       <c r="N3" t="n">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="O3" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="P3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.41</v>
+        <v>1.8</v>
       </c>
       <c r="S3" t="n">
-        <v>2.63</v>
+        <v>1.91</v>
       </c>
       <c r="T3" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="U3" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="V3" t="n">
-        <v>7.5</v>
+        <v>11</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.28</v>
+        <v>1.8</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.05</v>
+        <v>3.41</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.66</v>
+        <v>1.27</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.85</v>
+        <v>2.75</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.98</v>
+        <v>1.4</v>
       </c>
       <c r="AH3" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.38</v>
+        <v>3.2</v>
       </c>
       <c r="M4" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>2.55</v>
+        <v>2.13</v>
       </c>
       <c r="O4" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="P4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="U4" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.76</v>
+        <v>3.42</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.74</v>
+        <v>3.08</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.21</v>
+        <v>2.01</v>
       </c>
       <c r="AH4" t="n">
-        <v>5.1</v>
+        <v>6.05</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.2</v>
+        <v>2.38</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N5" t="n">
-        <v>2.13</v>
+        <v>2.55</v>
       </c>
       <c r="O5" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="P5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T5" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="V5" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.42</v>
+        <v>3.76</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.08</v>
+        <v>2.74</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.01</v>
+        <v>2.21</v>
       </c>
       <c r="AH5" t="n">
-        <v>6.05</v>
+        <v>5.1</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -2126,34 +2126,34 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -2168,34 +2168,34 @@
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -648,12 +648,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -674,76 +674,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="M2" t="n">
-        <v>3.11</v>
+        <v>2.5</v>
       </c>
       <c r="N2" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="O2" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="P2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.41</v>
+        <v>1.8</v>
       </c>
       <c r="S2" t="n">
-        <v>2.63</v>
+        <v>1.91</v>
       </c>
       <c r="T2" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="U2" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="V2" t="n">
-        <v>7.5</v>
+        <v>11</v>
       </c>
       <c r="W2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.28</v>
+        <v>1.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.05</v>
+        <v>3.75</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.66</v>
+        <v>1.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.85</v>
+        <v>2.75</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.98</v>
+        <v>1.4</v>
       </c>
       <c r="AH2" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="AL2" s="3" t="n">
-        <v>45883.45833333334</v>
+        <v>45883.5</v>
       </c>
     </row>
     <row r="3">
@@ -765,7 +765,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,77 +806,77 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="M3" t="n">
-        <v>2.42</v>
+        <v>2.75</v>
       </c>
       <c r="N3" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="O3" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="S3" t="n">
-        <v>1.91</v>
+        <v>2.43</v>
       </c>
       <c r="T3" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="V3" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="W3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI3" t="n">
         <v>1.02</v>
       </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ3" t="inlineStr">
         <is>
           <t>[]</t>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="AL3" s="3" t="n">
-        <v>45883.45833333334</v>
+        <v>45883.5</v>
       </c>
     </row>
     <row r="4">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,37 +938,37 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.2</v>
+        <v>2.29</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>2.13</v>
+        <v>2.46</v>
       </c>
       <c r="O4" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="P4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="T4" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="V4" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="W4" t="n">
         <v>1.1</v>
@@ -977,37 +977,37 @@
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.42</v>
+        <v>3.76</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.08</v>
+        <v>2.74</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.01</v>
+        <v>2.17</v>
       </c>
       <c r="AH4" t="n">
-        <v>6.05</v>
+        <v>5.1</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.38</v>
+        <v>3.05</v>
       </c>
       <c r="M5" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>2.55</v>
+        <v>2.08</v>
       </c>
       <c r="O5" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="P5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="S5" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="T5" t="n">
-        <v>2.48</v>
+        <v>2.68</v>
       </c>
       <c r="U5" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="V5" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>13</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.76</v>
+        <v>3.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="M6" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="N6" t="n">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="O6" t="n">
         <v>1.4</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AD6" t="n">
         <v>2</v>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.37</v>
+        <v>2.12</v>
       </c>
       <c r="M7" t="n">
-        <v>3.89</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>7.4</v>
+        <v>2.75</v>
       </c>
       <c r="O7" t="n">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="P7" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="S7" t="n">
-        <v>2.76</v>
+        <v>3.5</v>
       </c>
       <c r="T7" t="n">
-        <v>2.89</v>
+        <v>2.25</v>
       </c>
       <c r="U7" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="V7" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.96</v>
+        <v>1.57</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.74</v>
+        <v>2.35</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.5</v>
+        <v>2.33</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.27</v>
+        <v>1.53</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.55</v>
+        <v>2.38</v>
       </c>
       <c r="AH7" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>45883.58333333334</v>
+        <v>45883.60416666666</v>
       </c>
     </row>
     <row r="8">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,77 +1466,77 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.35</v>
+        <v>5.62</v>
       </c>
       <c r="M8" t="n">
-        <v>2.65</v>
+        <v>3.56</v>
       </c>
       <c r="N8" t="n">
-        <v>2.45</v>
+        <v>1.47</v>
       </c>
       <c r="O8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AD8" t="n">
         <v>2.55</v>
       </c>
-      <c r="P8" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V8" t="n">
-        <v>12</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X8" t="n">
+      <c r="AE8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AI8" t="n">
         <v>1.15</v>
       </c>
-      <c r="Y8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AJ8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>45883.58333333334</v>
+        <v>45883.61458333334</v>
       </c>
     </row>
     <row r="9">
@@ -1557,12 +1557,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P9" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Q9" t="n">
         <v>1.95</v>
       </c>
-      <c r="M9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.29</v>
+        <v>1.65</v>
       </c>
       <c r="S9" t="n">
-        <v>3.5</v>
+        <v>2.06</v>
       </c>
       <c r="T9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V9" t="n">
+        <v>12</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AA9" t="n">
         <v>2.25</v>
       </c>
-      <c r="U9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V9" t="n">
-        <v>5</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
       <c r="AB9" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.55</v>
       </c>
-      <c r="AC9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>45883.60416666666</v>
+        <v>45883.625</v>
       </c>
     </row>
     <row r="10">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>6.3</v>
+        <v>1.4</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="N10" t="n">
-        <v>1.52</v>
+        <v>7.25</v>
       </c>
       <c r="O10" t="n">
-        <v>2.88</v>
+        <v>1.38</v>
       </c>
       <c r="P10" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.44</v>
+        <v>3.9</v>
       </c>
       <c r="R10" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="S10" t="n">
-        <v>3.3</v>
+        <v>2.76</v>
       </c>
       <c r="T10" t="n">
-        <v>2.25</v>
+        <v>2.89</v>
       </c>
       <c r="U10" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="V10" t="n">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
         <v>9</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.1</v>
+        <v>3.08</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.55</v>
+        <v>3.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.72</v>
+        <v>2.37</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.97</v>
+        <v>1.54</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>45883.61458333334</v>
+        <v>45883.625</v>
       </c>
     </row>
     <row r="11">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="N11" t="n">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.37</v>
+        <v>3.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="N12" t="n">
-        <v>9</v>
+        <v>7.1</v>
       </c>
       <c r="O12" t="n">
         <v>1.36</v>
@@ -2036,19 +2036,19 @@
         <v>9.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AA12" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD12" t="n">
         <v>3.4</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>3.45</v>
       </c>
       <c r="AE12" t="n">
         <v>1.3</v>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="M14" t="n">
-        <v>2.85</v>
+        <v>3.21</v>
       </c>
       <c r="N14" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="O14" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="P14" t="n">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="R14" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="T14" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="U14" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.63</v>
+        <v>1.42</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.28</v>
+        <v>2.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.58</v>
+        <v>2.12</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="AD14" t="n">
-        <v>6.25</v>
+        <v>4.33</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AH14" t="n">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.91</v>
+        <v>4.1</v>
       </c>
       <c r="M15" t="n">
-        <v>3.21</v>
+        <v>2.85</v>
       </c>
       <c r="N15" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="O15" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="P15" t="n">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R15" t="n">
         <v>1.67</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V15" t="n">
+        <v>15</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AC15" t="n">
         <v>1.44</v>
       </c>
-      <c r="S15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V15" t="n">
-        <v>9</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AD15" t="n">
-        <v>4.33</v>
+        <v>6.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2540,19 +2540,19 @@
         <v>2.62</v>
       </c>
       <c r="R16" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="T16" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="U16" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="V16" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W16" t="n">
         <v>1.03</v>
@@ -2564,28 +2564,28 @@
         <v>5</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AB16" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AD16" t="n">
         <v>6.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF16" t="n">
         <v>2.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AH16" t="n">
         <v>11</v>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M11" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="N11" t="n">
-        <v>9</v>
+        <v>7.1</v>
       </c>
       <c r="O11" t="n">
         <v>1.36</v>
@@ -1904,19 +1904,19 @@
         <v>9.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AA11" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD11" t="n">
         <v>3.4</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>3.45</v>
       </c>
       <c r="AE11" t="n">
         <v>1.3</v>
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M12" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="N12" t="n">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="O12" t="n">
         <v>1.36</v>
@@ -2036,19 +2036,19 @@
         <v>9.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.37</v>
+        <v>3.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AE12" t="n">
         <v>1.3</v>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.91</v>
+        <v>4.1</v>
       </c>
       <c r="M14" t="n">
-        <v>3.21</v>
+        <v>2.85</v>
       </c>
       <c r="N14" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="O14" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="P14" t="n">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R14" t="n">
         <v>1.67</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V14" t="n">
+        <v>15</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AC14" t="n">
         <v>1.44</v>
       </c>
-      <c r="S14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V14" t="n">
-        <v>9</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AD14" t="n">
-        <v>4.33</v>
+        <v>6.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="M15" t="n">
-        <v>2.85</v>
+        <v>3.21</v>
       </c>
       <c r="N15" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="O15" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="P15" t="n">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="R15" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="T15" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="U15" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.63</v>
+        <v>1.42</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.28</v>
+        <v>2.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.58</v>
+        <v>2.12</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="AD15" t="n">
-        <v>6.25</v>
+        <v>4.33</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AH15" t="n">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -648,12 +648,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -674,76 +674,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.3</v>
+        <v>2.38</v>
       </c>
       <c r="M2" t="n">
-        <v>2.5</v>
+        <v>3.45</v>
       </c>
       <c r="N2" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O2" t="n">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>1.91</v>
+        <v>2.85</v>
       </c>
       <c r="T2" t="n">
-        <v>5</v>
+        <v>2.45</v>
       </c>
       <c r="U2" t="n">
-        <v>1.14</v>
+        <v>1.48</v>
       </c>
       <c r="V2" t="n">
-        <v>11</v>
+        <v>5.9</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.8</v>
+        <v>1.19</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.9</v>
+        <v>3.76</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.25</v>
+        <v>1.95</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.75</v>
+        <v>1.6</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.4</v>
+        <v>2.15</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.29</v>
+        <v>3.37</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5</v>
+        <v>2.42</v>
       </c>
       <c r="N4" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="O4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S4" t="n">
         <v>1.91</v>
       </c>
-      <c r="P4" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.85</v>
-      </c>
       <c r="T4" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="U4" t="n">
-        <v>1.45</v>
+        <v>1.14</v>
       </c>
       <c r="V4" t="n">
-        <v>5.9</v>
+        <v>11</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.19</v>
+        <v>1.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.76</v>
+        <v>1.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.72</v>
+        <v>3.41</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.99</v>
+        <v>1.27</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.58</v>
+        <v>2.75</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.17</v>
+        <v>1.4</v>
       </c>
       <c r="AH4" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="M5" t="n">
         <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="O5" t="n">
         <v>2.2</v>
@@ -1088,58 +1088,58 @@
         <v>1.8</v>
       </c>
       <c r="R5" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="S5" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="T5" t="n">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V5" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="W5" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.550000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC5" t="n">
         <v>1.85</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG5" t="n">
         <v>2</v>
       </c>
       <c r="AH5" t="n">
-        <v>5.3</v>
+        <v>6.55</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>5.62</v>
+        <v>6.3</v>
       </c>
       <c r="M8" t="n">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="O8" t="n">
         <v>2.88</v>
@@ -1484,58 +1484,58 @@
         <v>1.44</v>
       </c>
       <c r="R8" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="T8" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="U8" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="V8" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
         <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.94</v>
+        <v>3.82</v>
       </c>
       <c r="AB8" t="n">
         <v>1.65</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="AH8" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="M9" t="n">
         <v>2.65</v>
       </c>
       <c r="N9" t="n">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="O9" t="n">
         <v>2.55</v>
@@ -1640,7 +1640,7 @@
         <v>5.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AA9" t="n">
         <v>2.25</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="M10" t="n">
-        <v>4.2</v>
+        <v>3.89</v>
       </c>
       <c r="N10" t="n">
-        <v>7.25</v>
+        <v>7.4</v>
       </c>
       <c r="O10" t="n">
         <v>1.38</v>
@@ -1778,10 +1778,10 @@
         <v>3.08</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AD10" t="n">
         <v>3.5</v>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="M14" t="n">
-        <v>2.85</v>
+        <v>3.21</v>
       </c>
       <c r="N14" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="O14" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="P14" t="n">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="R14" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="T14" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="U14" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.63</v>
+        <v>1.42</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.28</v>
+        <v>2.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.58</v>
+        <v>2.12</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="AD14" t="n">
-        <v>6.25</v>
+        <v>4.33</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AH14" t="n">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.91</v>
+        <v>4.1</v>
       </c>
       <c r="M15" t="n">
-        <v>3.21</v>
+        <v>2.85</v>
       </c>
       <c r="N15" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="O15" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="P15" t="n">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R15" t="n">
         <v>1.67</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V15" t="n">
+        <v>15</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AC15" t="n">
         <v>1.44</v>
       </c>
-      <c r="S15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V15" t="n">
-        <v>9</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AD15" t="n">
-        <v>4.33</v>
+        <v>6.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL16"/>
+  <dimension ref="A1:AO16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,115 +513,130 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Odd_D_HT</t>
+          <t>Odd_A_HT</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Odd_A_HT</t>
+          <t>HT_Odd_Over05</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over05</t>
+          <t>HT_Odd_Under05</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under05</t>
+          <t>HT_Odd_Over15</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over15</t>
+          <t>HT_Odd_Under15</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under15</t>
+          <t>FT_Odd_Over05</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over25</t>
+          <t>Odd_Over15</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under25</t>
+          <t>Odd_Under15</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>FT_Odd_Over05</t>
+          <t>Odd_Over25</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>FT_Odd_Under05</t>
+          <t>Odd_Under25</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over15</t>
+          <t>Odd_Over35</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under15</t>
+          <t>Odd_Under35</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over25</t>
+          <t>Odd_BTTS_Yes</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under25</t>
+          <t>Odd_BTTS_No</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over35</t>
+          <t>homeGoals</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under35</t>
+          <t>awayGoals</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Odd_BTTS_Yes</t>
+          <t>Odd_H_D</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Odd_BTTS_No</t>
+          <t>Odd_A_D</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over45</t>
+          <t>Odd_H_HT1</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under45</t>
+          <t>Odd_D_HT1</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>homeGoals</t>
+          <t>Odd_A_HT1</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>awayGoals</t>
+          <t>Odd_DNB_H</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_DNB_A</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_marcar_prim_H</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_marcar_prim_A</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -686,76 +701,85 @@
         <v>1.91</v>
       </c>
       <c r="P2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W2" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AN2" t="n">
         <v>2</v>
       </c>
-      <c r="R2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL2" s="3" t="n">
+      <c r="AO2" s="3" t="n">
         <v>45883.5</v>
       </c>
     </row>
@@ -818,76 +842,85 @@
         <v>2.45</v>
       </c>
       <c r="P3" t="n">
-        <v>7</v>
+        <v>1.83</v>
       </c>
       <c r="Q3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AN3" t="n">
         <v>1.83</v>
       </c>
-      <c r="R3" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V3" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL3" s="3" t="n">
+      <c r="AO3" s="3" t="n">
         <v>45883.5</v>
       </c>
     </row>
@@ -950,76 +983,85 @@
         <v>2.6</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AN4" t="n">
         <v>2.05</v>
       </c>
-      <c r="R4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="T4" t="n">
-        <v>5</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="V4" t="n">
-        <v>11</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL4" s="3" t="n">
+      <c r="AO4" s="3" t="n">
         <v>45883.5</v>
       </c>
     </row>
@@ -1082,76 +1124,85 @@
         <v>2.2</v>
       </c>
       <c r="P5" t="n">
-        <v>9</v>
+        <v>1.8</v>
       </c>
       <c r="Q5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AN5" t="n">
         <v>1.8</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V5" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL5" s="3" t="n">
+      <c r="AO5" s="3" t="n">
         <v>45883.5</v>
       </c>
     </row>
@@ -1214,76 +1265,85 @@
         <v>1.4</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="R6" t="n">
+        <v>4</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN6" t="n">
         <v>2.75</v>
       </c>
-      <c r="R6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V6" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL6" s="3" t="n">
+      <c r="AO6" s="3" t="n">
         <v>45883.52083333334</v>
       </c>
     </row>
@@ -1346,76 +1406,85 @@
         <v>1.8</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="R7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN7" t="n">
         <v>2</v>
       </c>
-      <c r="R7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V7" t="n">
-        <v>5</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL7" s="3" t="n">
+      <c r="AO7" s="3" t="n">
         <v>45883.60416666666</v>
       </c>
     </row>
@@ -1478,76 +1547,85 @@
         <v>2.88</v>
       </c>
       <c r="P8" t="n">
-        <v>10</v>
+        <v>1.44</v>
       </c>
       <c r="Q8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AN8" t="n">
         <v>1.44</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL8" s="3" t="n">
+      <c r="AO8" s="3" t="n">
         <v>45883.61458333334</v>
       </c>
     </row>
@@ -1610,76 +1688,85 @@
         <v>2.55</v>
       </c>
       <c r="P9" t="n">
-        <v>5.25</v>
+        <v>1.95</v>
       </c>
       <c r="Q9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AN9" t="n">
         <v>1.95</v>
       </c>
-      <c r="R9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V9" t="n">
-        <v>12</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL9" s="3" t="n">
+      <c r="AO9" s="3" t="n">
         <v>45883.625</v>
       </c>
     </row>
@@ -1742,76 +1829,85 @@
         <v>1.38</v>
       </c>
       <c r="P10" t="n">
-        <v>8.5</v>
+        <v>3.9</v>
       </c>
       <c r="Q10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W10" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN10" t="n">
         <v>3.9</v>
       </c>
-      <c r="R10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V10" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL10" s="3" t="n">
+      <c r="AO10" s="3" t="n">
         <v>45883.625</v>
       </c>
     </row>
@@ -1874,76 +1970,85 @@
         <v>1.36</v>
       </c>
       <c r="P11" t="n">
-        <v>9.5</v>
+        <v>3.5</v>
       </c>
       <c r="Q11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN11" t="n">
         <v>3.5</v>
       </c>
-      <c r="R11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V11" t="n">
-        <v>7</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL11" s="3" t="n">
+      <c r="AO11" s="3" t="n">
         <v>45883.79166666666</v>
       </c>
     </row>
@@ -2006,76 +2111,85 @@
         <v>1.36</v>
       </c>
       <c r="P12" t="n">
-        <v>9.5</v>
+        <v>3.5</v>
       </c>
       <c r="Q12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R12" t="n">
+        <v>3</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN12" t="n">
         <v>3.5</v>
       </c>
-      <c r="R12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V12" t="n">
-        <v>7</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL12" s="3" t="n">
+      <c r="AO12" s="3" t="n">
         <v>45883.79166666666</v>
       </c>
     </row>
@@ -2138,76 +2252,85 @@
         <v>2.38</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="R13" t="n">
-        <v>1.22</v>
+        <v>3.6</v>
       </c>
       <c r="S13" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="U13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.11</v>
+        <v>1.93</v>
       </c>
       <c r="AA13" t="n">
-        <v>5</v>
+        <v>1.72</v>
       </c>
       <c r="AB13" t="n">
         <v>1.37</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.72</v>
+        <v>2.65</v>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF13" t="n">
-        <v>1.37</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.65</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL13" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AO13" s="3" t="n">
         <v>45883.83333333334</v>
       </c>
     </row>
@@ -2270,76 +2393,85 @@
         <v>2.6</v>
       </c>
       <c r="P14" t="n">
-        <v>7.5</v>
+        <v>1.67</v>
       </c>
       <c r="Q14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AN14" t="n">
         <v>1.67</v>
       </c>
-      <c r="R14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V14" t="n">
-        <v>9</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL14" s="3" t="n">
+      <c r="AO14" s="3" t="n">
         <v>45883.89583333334</v>
       </c>
     </row>
@@ -2402,76 +2534,85 @@
         <v>2.75</v>
       </c>
       <c r="P15" t="n">
-        <v>5.75</v>
+        <v>1.73</v>
       </c>
       <c r="Q15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AN15" t="n">
         <v>1.73</v>
       </c>
-      <c r="R15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>4</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V15" t="n">
-        <v>15</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL15" s="3" t="n">
+      <c r="AO15" s="3" t="n">
         <v>45883.89583333334</v>
       </c>
     </row>
@@ -2534,76 +2675,85 @@
         <v>1.95</v>
       </c>
       <c r="P16" t="n">
-        <v>5</v>
+        <v>2.62</v>
       </c>
       <c r="Q16" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AN16" t="n">
         <v>2.62</v>
       </c>
-      <c r="R16" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V16" t="n">
-        <v>13</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL16" s="3" t="n">
+      <c r="AO16" s="3" t="n">
         <v>45883.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -689,58 +689,58 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.38</v>
+        <v>3.37</v>
       </c>
       <c r="M2" t="n">
-        <v>3.45</v>
+        <v>2.42</v>
       </c>
       <c r="N2" t="n">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="O2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R2" t="n">
         <v>1.91</v>
       </c>
-      <c r="P2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.85</v>
-      </c>
       <c r="S2" t="n">
-        <v>2.45</v>
+        <v>5</v>
       </c>
       <c r="T2" t="n">
-        <v>1.48</v>
+        <v>1.14</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.19</v>
+        <v>1.8</v>
       </c>
       <c r="W2" t="n">
-        <v>3.76</v>
+        <v>1.9</v>
       </c>
       <c r="X2" t="n">
-        <v>1.7</v>
+        <v>3.41</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.95</v>
+        <v>1.27</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.6</v>
+        <v>2.75</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.15</v>
+        <v>1.4</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
@@ -753,19 +753,19 @@
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.92</v>
+        <v>4.33</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.19</v>
+        <v>1.73</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
@@ -774,10 +774,10 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="AN2" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AO2" s="3" t="n">
         <v>45883.5</v>
@@ -935,7 +935,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -971,95 +971,95 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.37</v>
+        <v>2.38</v>
       </c>
       <c r="M4" t="n">
-        <v>2.42</v>
+        <v>3.45</v>
       </c>
       <c r="N4" t="n">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="O4" t="n">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="P4" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="R4" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
         <v>1.91</v>
       </c>
-      <c r="S4" t="n">
-        <v>5</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="X4" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AN4" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AO4" s="3" t="n">
         <v>45883.5</v>
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="M6" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="N6" t="n">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="O6" t="n">
         <v>1.4</v>
@@ -1268,31 +1268,31 @@
         <v>2.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="R6" t="n">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="T6" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X6" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="Z6" t="n">
         <v>2</v>
@@ -1317,19 +1317,19 @@
         </is>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.83</v>
+        <v>1.52</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AJ6" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N7" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="O7" t="n">
         <v>1.8</v>
@@ -1409,31 +1409,31 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="R7" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="S7" t="n">
         <v>2.25</v>
       </c>
       <c r="T7" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="X7" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Z7" t="n">
         <v>2.33</v>
@@ -1442,10 +1442,10 @@
         <v>1.53</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -1458,19 +1458,19 @@
         </is>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH7" t="n">
         <v>2.75</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AJ7" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
@@ -1958,13 +1958,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="N11" t="n">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="O11" t="n">
         <v>1.36</v>
@@ -1988,19 +1988,19 @@
         <v>1.05</v>
       </c>
       <c r="V11" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="W11" t="n">
-        <v>2.37</v>
+        <v>3.4</v>
       </c>
       <c r="X11" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AA11" t="n">
         <v>1.3</v>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AG11" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AI11" t="n">
         <v>2.38</v>
       </c>
       <c r="AJ11" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="N12" t="n">
-        <v>9</v>
+        <v>7.1</v>
       </c>
       <c r="O12" t="n">
         <v>1.36</v>
@@ -2129,19 +2129,19 @@
         <v>1.05</v>
       </c>
       <c r="V12" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="W12" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Z12" t="n">
         <v>3.4</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.45</v>
       </c>
       <c r="AA12" t="n">
         <v>1.3</v>
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AI12" t="n">
         <v>2.38</v>
       </c>
       <c r="AJ12" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,83 +2381,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.91</v>
+        <v>4.1</v>
       </c>
       <c r="M14" t="n">
-        <v>3.21</v>
+        <v>2.85</v>
       </c>
       <c r="N14" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="O14" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="P14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q14" t="n">
         <v>1.67</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Y14" t="n">
         <v>1.44</v>
       </c>
-      <c r="R14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.72</v>
-      </c>
       <c r="Z14" t="n">
-        <v>4.33</v>
+        <v>6.25</v>
       </c>
       <c r="AA14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.2</v>
       </c>
-      <c r="AB14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH14" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45883.89583333334</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,95 +2522,95 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="M15" t="n">
-        <v>2.85</v>
+        <v>3.21</v>
       </c>
       <c r="N15" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="O15" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="P15" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="Q15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AN15" t="n">
         <v>1.67</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>4</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.73</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45883.89583333334</v>
@@ -2678,7 +2678,7 @@
         <v>2.62</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="R16" t="n">
         <v>2.1</v>
@@ -2687,22 +2687,22 @@
         <v>4.45</v>
       </c>
       <c r="T16" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="V16" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="W16" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="X16" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
         <v>6.5</v>
@@ -2711,10 +2711,10 @@
         <v>1.04</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -2730,16 +2730,16 @@
         <v>1.25</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AI16" t="n">
         <v>1.76</v>
       </c>
       <c r="AJ16" t="n">
-        <v>4.82</v>
+        <v>5</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -689,95 +689,95 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.37</v>
+        <v>2.38</v>
       </c>
       <c r="M2" t="n">
-        <v>2.42</v>
+        <v>3.45</v>
       </c>
       <c r="N2" t="n">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="O2" t="n">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="P2" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="R2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W2" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
         <v>1.91</v>
       </c>
-      <c r="S2" t="n">
-        <v>5</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="X2" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AN2" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AO2" s="3" t="n">
         <v>45883.5</v>
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -830,84 +830,84 @@
         </is>
       </c>
       <c r="L3" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>3.4</v>
       </c>
-      <c r="M3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>2.85</v>
-      </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
@@ -915,10 +915,10 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AO3" s="3" t="n">
         <v>45883.5</v>
@@ -935,7 +935,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -971,95 +971,95 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.38</v>
+        <v>3.4</v>
       </c>
       <c r="M4" t="n">
-        <v>3.45</v>
+        <v>2.75</v>
       </c>
       <c r="N4" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="P4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AB4" t="n">
         <v>2</v>
       </c>
-      <c r="Q4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="R4" t="n">
+      <c r="AC4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>2.85</v>
       </c>
-      <c r="S4" t="n">
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
         <v>2.45</v>
       </c>
-      <c r="T4" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W4" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AN4" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AO4" s="3" t="n">
         <v>45883.5</v>
@@ -1958,13 +1958,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M11" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="N11" t="n">
-        <v>9</v>
+        <v>7.1</v>
       </c>
       <c r="O11" t="n">
         <v>1.36</v>
@@ -1988,19 +1988,19 @@
         <v>1.05</v>
       </c>
       <c r="V11" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="W11" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Z11" t="n">
         <v>3.4</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.45</v>
       </c>
       <c r="AA11" t="n">
         <v>1.3</v>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AI11" t="n">
         <v>2.38</v>
       </c>
       <c r="AJ11" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M12" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="N12" t="n">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="O12" t="n">
         <v>1.36</v>
@@ -2129,19 +2129,19 @@
         <v>1.05</v>
       </c>
       <c r="V12" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="W12" t="n">
-        <v>2.37</v>
+        <v>3.4</v>
       </c>
       <c r="X12" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AA12" t="n">
         <v>1.3</v>
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AG12" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AI12" t="n">
         <v>2.38</v>
       </c>
       <c r="AJ12" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -704,7 +704,7 @@
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="R2" t="n">
         <v>2.85</v>
@@ -713,16 +713,16 @@
         <v>2.45</v>
       </c>
       <c r="T2" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="U2" t="n">
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W2" t="n">
-        <v>3.76</v>
+        <v>3.8</v>
       </c>
       <c r="X2" t="n">
         <v>1.7</v>
@@ -737,10 +737,10 @@
         <v>1.35</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
@@ -753,19 +753,19 @@
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="AI2" t="n">
         <v>2.19</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -830,83 +830,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.37</v>
+        <v>3.45</v>
       </c>
       <c r="M3" t="n">
-        <v>2.42</v>
+        <v>2.91</v>
       </c>
       <c r="N3" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="O3" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="P3" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="Q3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC3" t="n">
         <v>1.8</v>
       </c>
-      <c r="R3" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="S3" t="n">
-        <v>5</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="X3" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="Y3" t="n">
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG3" t="n">
         <v>1.27</v>
       </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
       <c r="AH3" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
@@ -915,10 +915,10 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AO3" s="3" t="n">
         <v>45883.5</v>
@@ -935,7 +935,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -971,59 +971,59 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="M4" t="n">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="O4" t="n">
         <v>2.2</v>
       </c>
-      <c r="O4" t="n">
-        <v>2.45</v>
-      </c>
       <c r="P4" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="R4" t="n">
-        <v>2.43</v>
+        <v>2.8</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="U4" t="n">
         <v>1.06</v>
       </c>
       <c r="V4" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="W4" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="X4" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.9</v>
+        <v>3.28</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AB4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC4" t="n">
         <v>2</v>
       </c>
-      <c r="AC4" t="n">
-        <v>1.79</v>
-      </c>
       <c r="AD4" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1035,19 +1035,19 @@
         </is>
       </c>
       <c r="AF4" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
@@ -1056,10 +1056,10 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AO4" s="3" t="n">
         <v>45883.5</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1112,58 +1112,58 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.2</v>
+        <v>3.37</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>2.42</v>
       </c>
       <c r="N5" t="n">
-        <v>2.13</v>
+        <v>2.44</v>
       </c>
       <c r="O5" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="P5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q5" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q5" t="n">
-        <v>1.41</v>
-      </c>
       <c r="R5" t="n">
-        <v>2.8</v>
+        <v>1.91</v>
       </c>
       <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
         <v>2.75</v>
       </c>
-      <c r="T5" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AC5" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
@@ -1176,31 +1176,31 @@
         </is>
       </c>
       <c r="AF5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="AI5" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AN5" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.8</v>
       </c>
       <c r="AO5" s="3" t="n">
         <v>45883.5</v>
@@ -1274,7 +1274,7 @@
         <v>3.84</v>
       </c>
       <c r="S6" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="T6" t="n">
         <v>1.7</v>
@@ -1283,7 +1283,7 @@
         <v>1.02</v>
       </c>
       <c r="V6" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="W6" t="n">
         <v>6</v>
@@ -1301,10 +1301,10 @@
         <v>1.72</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -1317,19 +1317,19 @@
         </is>
       </c>
       <c r="AF6" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AG6" t="n">
         <v>3.1</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="AJ6" t="n">
-        <v>7</v>
+        <v>6.35</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
@@ -1409,16 +1409,16 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="R7" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="S7" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="T7" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="U7" t="n">
         <v>1.02</v>
@@ -1427,7 +1427,7 @@
         <v>1.18</v>
       </c>
       <c r="W7" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="X7" t="n">
         <v>1.55</v>
@@ -1442,10 +1442,10 @@
         <v>1.53</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -1458,19 +1458,19 @@
         </is>
       </c>
       <c r="AF7" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.75</v>
+        <v>3.09</v>
       </c>
       <c r="AI7" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="AJ7" t="n">
-        <v>3.4</v>
+        <v>3.07</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
@@ -1550,25 +1550,25 @@
         <v>1.44</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="R8" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="S8" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="T8" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="U8" t="n">
         <v>1</v>
       </c>
       <c r="V8" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="W8" t="n">
-        <v>3.82</v>
+        <v>4.3</v>
       </c>
       <c r="X8" t="n">
         <v>1.65</v>
@@ -1577,16 +1577,16 @@
         <v>2.1</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
@@ -1599,19 +1599,19 @@
         </is>
       </c>
       <c r="AF8" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AH8" t="n">
-        <v>6.5</v>
+        <v>7.7</v>
       </c>
       <c r="AI8" t="n">
         <v>2.35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,58 +1676,58 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.35</v>
+        <v>1.37</v>
       </c>
       <c r="M9" t="n">
-        <v>2.65</v>
+        <v>3.89</v>
       </c>
       <c r="N9" t="n">
-        <v>2.45</v>
+        <v>7.4</v>
       </c>
       <c r="O9" t="n">
-        <v>2.55</v>
+        <v>1.38</v>
       </c>
       <c r="P9" t="n">
-        <v>1.95</v>
+        <v>3.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="R9" t="n">
-        <v>2.06</v>
+        <v>2.9</v>
       </c>
       <c r="S9" t="n">
-        <v>3.8</v>
+        <v>2.89</v>
       </c>
       <c r="T9" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="U9" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="V9" t="n">
-        <v>1.58</v>
+        <v>1.27</v>
       </c>
       <c r="W9" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="X9" t="n">
-        <v>2.85</v>
+        <v>1.96</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.37</v>
+        <v>1.74</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -1740,19 +1740,19 @@
         </is>
       </c>
       <c r="AF9" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>3.03</v>
       </c>
       <c r="AH9" t="n">
-        <v>4</v>
+        <v>1.88</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.91</v>
+        <v>2.35</v>
       </c>
       <c r="AJ9" t="n">
-        <v>3.18</v>
+        <v>7</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>2.55</v>
+        <v>1.38</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.95</v>
+        <v>3.9</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>45883.625</v>
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1817,58 +1817,58 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.37</v>
       </c>
-      <c r="M10" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="N10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W10" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.74</v>
-      </c>
       <c r="Z10" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -1881,19 +1881,19 @@
         </is>
       </c>
       <c r="AF10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.22</v>
       </c>
-      <c r="AG10" t="n">
-        <v>3.02</v>
-      </c>
       <c r="AH10" t="n">
-        <v>1.67</v>
+        <v>4.2</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AJ10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
@@ -1902,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.38</v>
+        <v>2.55</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.9</v>
+        <v>1.95</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>45883.625</v>
@@ -1958,13 +1958,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="N11" t="n">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="O11" t="n">
         <v>1.36</v>
@@ -1988,19 +1988,19 @@
         <v>1.05</v>
       </c>
       <c r="V11" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="W11" t="n">
-        <v>2.37</v>
+        <v>3.4</v>
       </c>
       <c r="X11" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AA11" t="n">
         <v>1.3</v>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AG11" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AI11" t="n">
         <v>2.38</v>
       </c>
       <c r="AJ11" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="N12" t="n">
-        <v>9</v>
+        <v>7.1</v>
       </c>
       <c r="O12" t="n">
         <v>1.36</v>
@@ -2129,19 +2129,19 @@
         <v>1.05</v>
       </c>
       <c r="V12" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="W12" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Z12" t="n">
         <v>3.4</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.45</v>
       </c>
       <c r="AA12" t="n">
         <v>1.3</v>
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AI12" t="n">
         <v>2.38</v>
       </c>
       <c r="AJ12" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2678,16 +2678,16 @@
         <v>2.62</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S16" t="n">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="T16" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="U16" t="n">
         <v>1.17</v>
@@ -2699,16 +2699,16 @@
         <v>2.15</v>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>3.27</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z16" t="n">
         <v>6.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AB16" t="n">
         <v>2.52</v>
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="AF16" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AH16" t="n">
         <v>3.15</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AJ16" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,58 +1676,58 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y9" t="n">
         <v>1.37</v>
       </c>
-      <c r="M9" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="N9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.74</v>
-      </c>
       <c r="Z9" t="n">
-        <v>3.2</v>
+        <v>5.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -1740,19 +1740,19 @@
         </is>
       </c>
       <c r="AF9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.22</v>
       </c>
-      <c r="AG9" t="n">
-        <v>3.03</v>
-      </c>
       <c r="AH9" t="n">
-        <v>1.88</v>
+        <v>4.2</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="AJ9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.38</v>
+        <v>2.55</v>
       </c>
       <c r="AN9" t="n">
-        <v>3.9</v>
+        <v>1.95</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>45883.625</v>
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1817,58 +1817,58 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.35</v>
+        <v>1.37</v>
       </c>
       <c r="M10" t="n">
-        <v>2.65</v>
+        <v>3.89</v>
       </c>
       <c r="N10" t="n">
-        <v>2.45</v>
+        <v>7.4</v>
       </c>
       <c r="O10" t="n">
-        <v>2.55</v>
+        <v>1.38</v>
       </c>
       <c r="P10" t="n">
-        <v>1.95</v>
+        <v>3.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="R10" t="n">
-        <v>2.05</v>
+        <v>2.9</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>2.89</v>
       </c>
       <c r="T10" t="n">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="U10" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="V10" t="n">
-        <v>1.58</v>
+        <v>1.27</v>
       </c>
       <c r="W10" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="X10" t="n">
-        <v>2.85</v>
+        <v>1.96</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.37</v>
+        <v>1.74</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -1881,19 +1881,19 @@
         </is>
       </c>
       <c r="AF10" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>3.03</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.2</v>
+        <v>1.88</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="AJ10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
@@ -1902,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>2.55</v>
+        <v>1.38</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.95</v>
+        <v>3.9</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>45883.625</v>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="M13" t="n">
-        <v>4.6</v>
+        <v>4.69</v>
       </c>
       <c r="N13" t="n">
         <v>1.8</v>
@@ -2261,10 +2261,10 @@
         <v>3.6</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="T13" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -2276,7 +2276,7 @@
         <v>5</v>
       </c>
       <c r="X13" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="Y13" t="n">
         <v>2.7</v>
@@ -2288,10 +2288,10 @@
         <v>1.72</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2304,19 +2304,19 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>1.24</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,95 +2381,95 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="M14" t="n">
-        <v>2.85</v>
+        <v>3.21</v>
       </c>
       <c r="N14" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="O14" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="P14" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="Q14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AN14" t="n">
         <v>1.67</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>4</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.73</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45883.89583333334</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,83 +2522,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.91</v>
+        <v>4.1</v>
       </c>
       <c r="M15" t="n">
-        <v>3.21</v>
+        <v>2.85</v>
       </c>
       <c r="N15" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="O15" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="P15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q15" t="n">
         <v>1.67</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Y15" t="n">
         <v>1.44</v>
       </c>
-      <c r="R15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.72</v>
-      </c>
       <c r="Z15" t="n">
-        <v>4.33</v>
+        <v>6.25</v>
       </c>
       <c r="AA15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.2</v>
       </c>
-      <c r="AB15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH15" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45883.89583333334</v>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -689,59 +689,59 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.38</v>
+        <v>3.2</v>
       </c>
       <c r="M2" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N2" t="n">
-        <v>2.55</v>
+        <v>2.13</v>
       </c>
       <c r="O2" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="P2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC2" t="n">
         <v>2</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.21</v>
-      </c>
       <c r="AD2" t="inlineStr">
         <is>
           <t>[]</t>
@@ -753,19 +753,19 @@
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
@@ -774,10 +774,10 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AN2" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AO2" s="3" t="n">
         <v>45883.5</v>
@@ -794,7 +794,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -830,58 +830,58 @@
         </is>
       </c>
       <c r="L3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="M3" t="n">
         <v>3.45</v>
       </c>
-      <c r="M3" t="n">
-        <v>2.91</v>
-      </c>
       <c r="N3" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="O3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="S3" t="n">
         <v>2.45</v>
       </c>
-      <c r="P3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="T3" t="n">
         <v>1.45</v>
       </c>
-      <c r="R3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.32</v>
-      </c>
       <c r="U3" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="W3" t="n">
-        <v>2.59</v>
+        <v>3.8</v>
       </c>
       <c r="X3" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.56</v>
+        <v>1.95</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.2</v>
+        <v>2.74</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.8</v>
+        <v>2.21</v>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
@@ -894,19 +894,19 @@
         </is>
       </c>
       <c r="AF3" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="AH3" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.7</v>
+        <v>2.19</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.9</v>
+        <v>3.16</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
@@ -915,10 +915,10 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AO3" s="3" t="n">
         <v>45883.5</v>
@@ -935,7 +935,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -971,95 +971,95 @@
         </is>
       </c>
       <c r="L4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>3.2</v>
       </c>
-      <c r="M4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="O4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AI4" t="n">
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AN4" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.8</v>
       </c>
       <c r="AO4" s="3" t="n">
         <v>45883.5</v>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1112,83 +1112,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="M5" t="n">
-        <v>2.42</v>
+        <v>2.88</v>
       </c>
       <c r="N5" t="n">
-        <v>2.44</v>
+        <v>2.18</v>
       </c>
       <c r="O5" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="P5" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="R5" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>3.42</v>
       </c>
       <c r="T5" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="W5" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB5" t="n">
         <v>1.9</v>
       </c>
-      <c r="X5" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="Y5" t="n">
+      <c r="AC5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AG5" t="n">
         <v>1.27</v>
       </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
       <c r="AH5" t="n">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AJ5" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
@@ -1197,10 +1197,10 @@
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AN5" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AO5" s="3" t="n">
         <v>45883.5</v>
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,83 +1676,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.35</v>
+        <v>1.4</v>
       </c>
       <c r="M9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N9" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="R9" t="n">
         <v>2.65</v>
       </c>
-      <c r="N9" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.05</v>
-      </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>3.04</v>
       </c>
       <c r="T9" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="U9" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="V9" t="n">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="W9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AI9" t="n">
         <v>2.25</v>
       </c>
-      <c r="X9" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AJ9" t="n">
-        <v>3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>2.55</v>
+        <v>1.38</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.95</v>
+        <v>3.9</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>45883.625</v>
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1817,58 +1817,58 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.37</v>
       </c>
-      <c r="M10" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="N10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.74</v>
-      </c>
       <c r="Z10" t="n">
-        <v>3.2</v>
+        <v>5.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -1881,19 +1881,19 @@
         </is>
       </c>
       <c r="AF10" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.03</v>
+        <v>1.13</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.88</v>
+        <v>4.6</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.35</v>
+        <v>1.57</v>
       </c>
       <c r="AJ10" t="n">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
@@ -1902,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.38</v>
+        <v>2.55</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.9</v>
+        <v>1.95</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>45883.625</v>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,83 +2381,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.91</v>
+        <v>4.1</v>
       </c>
       <c r="M14" t="n">
-        <v>3.21</v>
+        <v>2.85</v>
       </c>
       <c r="N14" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="O14" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="P14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q14" t="n">
         <v>1.67</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Y14" t="n">
         <v>1.44</v>
       </c>
-      <c r="R14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.72</v>
-      </c>
       <c r="Z14" t="n">
-        <v>4.33</v>
+        <v>6.25</v>
       </c>
       <c r="AA14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.2</v>
       </c>
-      <c r="AB14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH14" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45883.89583333334</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,95 +2522,95 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="M15" t="n">
-        <v>2.85</v>
+        <v>3.21</v>
       </c>
       <c r="N15" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="O15" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="P15" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="Q15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AN15" t="n">
         <v>1.67</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>4</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.73</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45883.89583333334</v>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -689,95 +689,95 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.2</v>
+        <v>2.38</v>
       </c>
       <c r="M2" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N2" t="n">
-        <v>2.13</v>
+        <v>2.55</v>
       </c>
       <c r="O2" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="R2" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="S2" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="U2" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W2" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="X2" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.28</v>
+        <v>2.74</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="AC2" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AN2" t="n">
         <v>2</v>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1.8</v>
       </c>
       <c r="AO2" s="3" t="n">
         <v>45883.5</v>
@@ -794,7 +794,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -830,95 +830,95 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.38</v>
+        <v>3.35</v>
       </c>
       <c r="M3" t="n">
-        <v>3.45</v>
+        <v>2.88</v>
       </c>
       <c r="N3" t="n">
-        <v>2.55</v>
+        <v>2.18</v>
       </c>
       <c r="O3" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="R3" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="S3" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
         <v>2.45</v>
       </c>
-      <c r="T3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AN3" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AO3" s="3" t="n">
         <v>45883.5</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1112,83 +1112,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="M5" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="O5" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="P5" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="R5" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="S5" t="n">
-        <v>3.42</v>
+        <v>2.7</v>
       </c>
       <c r="T5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA5" t="n">
         <v>1.27</v>
       </c>
-      <c r="U5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="V5" t="n">
+      <c r="AB5" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG5" t="n">
         <v>1.5</v>
       </c>
-      <c r="W5" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH5" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AJ5" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
@@ -1197,10 +1197,10 @@
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AO5" s="3" t="n">
         <v>45883.5</v>
@@ -1958,13 +1958,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M11" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="N11" t="n">
-        <v>9</v>
+        <v>7.1</v>
       </c>
       <c r="O11" t="n">
         <v>1.36</v>
@@ -1988,19 +1988,19 @@
         <v>1.05</v>
       </c>
       <c r="V11" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="W11" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Z11" t="n">
         <v>3.4</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.45</v>
       </c>
       <c r="AA11" t="n">
         <v>1.3</v>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AI11" t="n">
         <v>2.38</v>
       </c>
       <c r="AJ11" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M12" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="N12" t="n">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="O12" t="n">
         <v>1.36</v>
@@ -2129,19 +2129,19 @@
         <v>1.05</v>
       </c>
       <c r="V12" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="W12" t="n">
-        <v>2.37</v>
+        <v>3.4</v>
       </c>
       <c r="X12" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AA12" t="n">
         <v>1.3</v>
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AG12" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AI12" t="n">
         <v>2.38</v>
       </c>
       <c r="AJ12" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -689,83 +689,83 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.38</v>
+        <v>3.2</v>
       </c>
       <c r="M2" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N2" t="n">
-        <v>2.55</v>
+        <v>2.13</v>
       </c>
       <c r="O2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AI2" t="n">
         <v>1.91</v>
       </c>
-      <c r="P2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>2.19</v>
-      </c>
       <c r="AJ2" t="n">
-        <v>3.16</v>
+        <v>2.96</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
@@ -774,10 +774,10 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AN2" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AO2" s="3" t="n">
         <v>45883.5</v>
@@ -794,7 +794,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -830,83 +830,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.35</v>
+        <v>2.38</v>
       </c>
       <c r="M3" t="n">
-        <v>2.88</v>
+        <v>3.45</v>
       </c>
       <c r="N3" t="n">
-        <v>2.18</v>
+        <v>2.55</v>
       </c>
       <c r="O3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W3" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH3" t="n">
         <v>2.45</v>
       </c>
-      <c r="P3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AI3" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
@@ -915,10 +915,10 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AO3" s="3" t="n">
         <v>45883.5</v>
@@ -971,13 +971,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.65</v>
+        <v>3.37</v>
       </c>
       <c r="M4" t="n">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="N4" t="n">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="O4" t="n">
         <v>2.6</v>
@@ -1001,16 +1001,16 @@
         <v>1.14</v>
       </c>
       <c r="V4" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="X4" t="n">
-        <v>3</v>
+        <v>3.41</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z4" t="n">
         <v>5.8</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1112,84 +1112,84 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="N5" t="n">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="O5" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="R5" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="S5" t="n">
-        <v>2.7</v>
+        <v>3.42</v>
       </c>
       <c r="T5" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="U5" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="W5" t="n">
-        <v>3.25</v>
+        <v>2.46</v>
       </c>
       <c r="X5" t="n">
-        <v>1.85</v>
+        <v>2.35</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.28</v>
+        <v>4.2</v>
       </c>
       <c r="AA5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AG5" t="n">
         <v>1.27</v>
       </c>
-      <c r="AB5" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AH5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>3.1</v>
       </c>
-      <c r="AI5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
@@ -1197,10 +1197,10 @@
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AO5" s="3" t="n">
         <v>45883.5</v>
@@ -1286,7 +1286,7 @@
         <v>1.11</v>
       </c>
       <c r="W6" t="n">
-        <v>6</v>
+        <v>5.35</v>
       </c>
       <c r="X6" t="n">
         <v>1.45</v>
@@ -1301,10 +1301,10 @@
         <v>1.72</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -1317,19 +1317,19 @@
         </is>
       </c>
       <c r="AF6" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AG6" t="n">
         <v>3.1</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AI6" t="n">
         <v>2.69</v>
       </c>
       <c r="AJ6" t="n">
-        <v>6.35</v>
+        <v>6.58</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
@@ -1412,22 +1412,22 @@
         <v>1.26</v>
       </c>
       <c r="R7" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="S7" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="T7" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="U7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="V7" t="n">
         <v>1.18</v>
       </c>
       <c r="W7" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="X7" t="n">
         <v>1.55</v>
@@ -1442,10 +1442,10 @@
         <v>1.53</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -1458,19 +1458,19 @@
         </is>
       </c>
       <c r="AF7" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.44</v>
+        <v>1.97</v>
       </c>
       <c r="AJ7" t="n">
-        <v>3.07</v>
+        <v>2.93</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
@@ -1550,25 +1550,25 @@
         <v>1.44</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="R8" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="S8" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="T8" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="V8" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="W8" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="X8" t="n">
         <v>1.65</v>
@@ -1583,10 +1583,10 @@
         <v>1.42</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
@@ -1599,19 +1599,19 @@
         </is>
       </c>
       <c r="AF8" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AH8" t="n">
-        <v>7.7</v>
+        <v>6.9</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.35</v>
+        <v>2.26</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,58 +1676,58 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.4</v>
+        <v>3.35</v>
       </c>
       <c r="M9" t="n">
-        <v>3.9</v>
+        <v>2.65</v>
       </c>
       <c r="N9" t="n">
-        <v>8.1</v>
+        <v>2.45</v>
       </c>
       <c r="O9" t="n">
-        <v>1.38</v>
+        <v>2.55</v>
       </c>
       <c r="P9" t="n">
-        <v>3.9</v>
+        <v>1.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.42</v>
+        <v>1.68</v>
       </c>
       <c r="R9" t="n">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="S9" t="n">
-        <v>3.04</v>
+        <v>4</v>
       </c>
       <c r="T9" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="U9" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="W9" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="X9" t="n">
-        <v>2.19</v>
+        <v>2.85</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.82</v>
+        <v>5.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -1740,19 +1740,19 @@
         </is>
       </c>
       <c r="AF9" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.6</v>
+        <v>1.13</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.99</v>
+        <v>4.6</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="AJ9" t="n">
-        <v>8.300000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.38</v>
+        <v>2.55</v>
       </c>
       <c r="AN9" t="n">
-        <v>3.9</v>
+        <v>1.95</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>45883.625</v>
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1817,83 +1817,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.3</v>
+        <v>1.37</v>
       </c>
       <c r="M10" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="N10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AG10" t="n">
         <v>2.6</v>
       </c>
-      <c r="N10" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="W10" t="n">
+      <c r="AH10" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AI10" t="n">
         <v>2.25</v>
       </c>
-      <c r="X10" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AJ10" t="n">
-        <v>3.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
@@ -1902,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>2.55</v>
+        <v>1.38</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.95</v>
+        <v>3.9</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>45883.625</v>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,95 +2381,95 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="M14" t="n">
-        <v>2.85</v>
+        <v>3.21</v>
       </c>
       <c r="N14" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="O14" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="P14" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="Q14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AN14" t="n">
         <v>1.67</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>4</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.73</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45883.89583333334</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,83 +2522,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.91</v>
+        <v>4.1</v>
       </c>
       <c r="M15" t="n">
-        <v>3.21</v>
+        <v>2.85</v>
       </c>
       <c r="N15" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="O15" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="P15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q15" t="n">
         <v>1.67</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Y15" t="n">
         <v>1.44</v>
       </c>
-      <c r="R15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.72</v>
-      </c>
       <c r="Z15" t="n">
-        <v>4.33</v>
+        <v>6.25</v>
       </c>
       <c r="AA15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.2</v>
       </c>
-      <c r="AB15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH15" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45883.89583333334</v>
@@ -2678,16 +2678,16 @@
         <v>2.62</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R16" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="S16" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="T16" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="U16" t="n">
         <v>1.17</v>
@@ -2705,7 +2705,7 @@
         <v>1.29</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA16" t="n">
         <v>1.08</v>
@@ -2727,10 +2727,10 @@
         </is>
       </c>
       <c r="AF16" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AH16" t="n">
         <v>3.15</v>
@@ -2739,7 +2739,7 @@
         <v>1.74</v>
       </c>
       <c r="AJ16" t="n">
-        <v>4.7</v>
+        <v>4.98</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -689,58 +689,58 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.2</v>
+        <v>2.38</v>
       </c>
       <c r="M2" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N2" t="n">
-        <v>2.13</v>
+        <v>2.55</v>
       </c>
       <c r="O2" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="R2" t="n">
-        <v>2.49</v>
+        <v>2.9</v>
       </c>
       <c r="S2" t="n">
-        <v>3.04</v>
+        <v>2.68</v>
       </c>
       <c r="T2" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="U2" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="W2" t="n">
-        <v>2.83</v>
+        <v>3.28</v>
       </c>
       <c r="X2" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.2</v>
+        <v>3.08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
@@ -753,31 +753,31 @@
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.84</v>
+        <v>2.45</v>
       </c>
       <c r="AI2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
         <v>1.91</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AN2" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AO2" s="3" t="n">
         <v>45883.5</v>
@@ -794,7 +794,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -830,83 +830,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.38</v>
+        <v>2.78</v>
       </c>
       <c r="M3" t="n">
-        <v>3.45</v>
+        <v>2.77</v>
       </c>
       <c r="N3" t="n">
-        <v>2.55</v>
+        <v>1.99</v>
       </c>
       <c r="O3" t="n">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="P3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W3" t="n">
         <v>2</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W3" t="n">
-        <v>3.28</v>
-      </c>
       <c r="X3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AI3" t="n">
         <v>1.7</v>
       </c>
-      <c r="Y3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AJ3" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
@@ -915,10 +915,10 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="AN3" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AO3" s="3" t="n">
         <v>45883.5</v>
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -971,95 +971,95 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.37</v>
+        <v>2.97</v>
       </c>
       <c r="M4" t="n">
-        <v>2.42</v>
+        <v>2.7</v>
       </c>
       <c r="N4" t="n">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="O4" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="P4" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="R4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB4" t="n">
         <v>2.07</v>
       </c>
-      <c r="S4" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="X4" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB4" t="n">
+      <c r="AC4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
         <v>2.45</v>
       </c>
-      <c r="AC4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AN4" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AO4" s="3" t="n">
         <v>45883.5</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1112,58 +1112,58 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="M5" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="O5" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="P5" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q5" t="n">
         <v>1.45</v>
       </c>
       <c r="R5" t="n">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="S5" t="n">
-        <v>3.42</v>
+        <v>3.04</v>
       </c>
       <c r="T5" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="U5" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W5" t="n">
-        <v>2.46</v>
+        <v>2.83</v>
       </c>
       <c r="X5" t="n">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="Z5" t="n">
         <v>4.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
@@ -1176,19 +1176,19 @@
         </is>
       </c>
       <c r="AF5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AG5" t="n">
         <v>1.28</v>
       </c>
-      <c r="AG5" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH5" t="n">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AJ5" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
@@ -1197,10 +1197,10 @@
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AO5" s="3" t="n">
         <v>45883.5</v>
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,83 +1676,83 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M9" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="N9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AG9" t="n">
         <v>3.35</v>
       </c>
-      <c r="M9" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="W9" t="n">
+      <c r="AH9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI9" t="n">
         <v>2.25</v>
       </c>
-      <c r="X9" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AJ9" t="n">
-        <v>3.3</v>
+        <v>7.43</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>2.55</v>
+        <v>1.38</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.95</v>
+        <v>3.9</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>45883.625</v>
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1817,58 +1817,58 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.37</v>
+        <v>4.2</v>
       </c>
       <c r="M10" t="n">
-        <v>3.89</v>
+        <v>2.7</v>
       </c>
       <c r="N10" t="n">
-        <v>7.4</v>
+        <v>1.98</v>
       </c>
       <c r="O10" t="n">
-        <v>1.38</v>
+        <v>2.55</v>
       </c>
       <c r="P10" t="n">
-        <v>3.9</v>
+        <v>1.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="R10" t="n">
-        <v>2.65</v>
+        <v>2.15</v>
       </c>
       <c r="S10" t="n">
-        <v>3.04</v>
+        <v>4.1</v>
       </c>
       <c r="T10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.33</v>
       </c>
-      <c r="U10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.74</v>
-      </c>
       <c r="Z10" t="n">
-        <v>3.82</v>
+        <v>5.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -1881,19 +1881,19 @@
         </is>
       </c>
       <c r="AF10" t="n">
-        <v>1.22</v>
+        <v>1.7</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.6</v>
+        <v>1.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.99</v>
+        <v>4.8</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="AJ10" t="n">
-        <v>8.300000000000001</v>
+        <v>2.85</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
@@ -1902,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.38</v>
+        <v>2.55</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.9</v>
+        <v>1.95</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>45883.625</v>
@@ -1958,13 +1958,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="N11" t="n">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="O11" t="n">
         <v>1.36</v>
@@ -1988,19 +1988,19 @@
         <v>1.05</v>
       </c>
       <c r="V11" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="W11" t="n">
-        <v>2.37</v>
+        <v>3.4</v>
       </c>
       <c r="X11" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AA11" t="n">
         <v>1.3</v>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AG11" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AI11" t="n">
         <v>2.38</v>
       </c>
       <c r="AJ11" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="N12" t="n">
-        <v>9</v>
+        <v>7.1</v>
       </c>
       <c r="O12" t="n">
         <v>1.36</v>
@@ -2129,19 +2129,19 @@
         <v>1.05</v>
       </c>
       <c r="V12" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="W12" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Z12" t="n">
         <v>3.4</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.45</v>
       </c>
       <c r="AA12" t="n">
         <v>1.3</v>
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AI12" t="n">
         <v>2.38</v>
       </c>
       <c r="AJ12" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,83 +2381,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.91</v>
+        <v>4.1</v>
       </c>
       <c r="M14" t="n">
-        <v>3.21</v>
+        <v>2.85</v>
       </c>
       <c r="N14" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="O14" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="P14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q14" t="n">
         <v>1.67</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Y14" t="n">
         <v>1.44</v>
       </c>
-      <c r="R14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.72</v>
-      </c>
       <c r="Z14" t="n">
-        <v>4.33</v>
+        <v>6.25</v>
       </c>
       <c r="AA14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.2</v>
       </c>
-      <c r="AB14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH14" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45883.89583333334</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,95 +2522,95 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="M15" t="n">
-        <v>2.85</v>
+        <v>3.21</v>
       </c>
       <c r="N15" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="O15" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="P15" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="Q15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AN15" t="n">
         <v>1.67</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>4</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.73</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45883.89583333334</v>
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="M16" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="N16" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="O16" t="n">
         <v>1.95</v>
@@ -2678,40 +2678,40 @@
         <v>2.62</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="R16" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="S16" t="n">
-        <v>4.45</v>
+        <v>4.25</v>
       </c>
       <c r="T16" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="V16" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="W16" t="n">
         <v>2.15</v>
       </c>
       <c r="X16" t="n">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>7.5</v>
+        <v>6.91</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.52</v>
+        <v>2.47</v>
       </c>
       <c r="AC16" t="n">
         <v>1.5</v>
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="AF16" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AJ16" t="n">
-        <v>4.98</v>
+        <v>4.5</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -685,99 +685,99 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.38</v>
+        <v>2.97</v>
       </c>
       <c r="M2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH2" t="n">
         <v>3.45</v>
       </c>
-      <c r="N2" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W2" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH2" t="n">
+      <c r="AI2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
         <v>2.45</v>
       </c>
-      <c r="AI2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AN2" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AO2" s="3" t="n">
         <v>45883.5</v>
@@ -813,20 +813,20 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -885,12 +885,12 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+1']</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5', '45+6']</t>
         </is>
       </c>
       <c r="AF3" t="n">
@@ -935,7 +935,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -967,87 +967,87 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.97</v>
+        <v>2.1</v>
       </c>
       <c r="M4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AH4" t="n">
         <v>2.7</v>
       </c>
-      <c r="N4" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="O4" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>3.45</v>
-      </c>
       <c r="AI4" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
@@ -1056,10 +1056,10 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AO4" s="3" t="n">
         <v>45883.5</v>
@@ -1098,27 +1098,27 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.2</v>
+        <v>2.35</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="N5" t="n">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="O5" t="n">
         <v>2.2</v>
@@ -1127,43 +1127,43 @@
         <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="R5" t="n">
-        <v>2.49</v>
+        <v>2.65</v>
       </c>
       <c r="S5" t="n">
-        <v>3.04</v>
+        <v>2.95</v>
       </c>
       <c r="T5" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="U5" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W5" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="X5" t="n">
-        <v>1.85</v>
+        <v>2.11</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.2</v>
+        <v>3.88</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
@@ -1172,20 +1172,20 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2']</t>
         </is>
       </c>
       <c r="AF5" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.84</v>
+        <v>3.3</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AJ5" t="n">
         <v>2.96</v>
@@ -1236,30 +1236,30 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M6" t="n">
-        <v>5.1</v>
+        <v>5.15</v>
       </c>
       <c r="N6" t="n">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="O6" t="n">
         <v>1.4</v>
@@ -1268,16 +1268,16 @@
         <v>2.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="R6" t="n">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="S6" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="U6" t="n">
         <v>1.02</v>
@@ -1286,50 +1286,50 @@
         <v>1.11</v>
       </c>
       <c r="W6" t="n">
-        <v>5.35</v>
+        <v>5.3</v>
       </c>
       <c r="X6" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['68', '82', '90']</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['20']</t>
         </is>
       </c>
       <c r="AF6" t="n">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="AG6" t="n">
         <v>3.1</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="AJ6" t="n">
-        <v>6.58</v>
+        <v>5.7</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.95</v>
+        <v>2.37</v>
       </c>
       <c r="M7" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N7" t="n">
-        <v>3.25</v>
+        <v>2.82</v>
       </c>
       <c r="O7" t="n">
         <v>1.8</v>
@@ -1409,13 +1409,13 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="R7" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="S7" t="n">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="T7" t="n">
         <v>1.55</v>
@@ -1427,50 +1427,50 @@
         <v>1.18</v>
       </c>
       <c r="W7" t="n">
-        <v>4.75</v>
+        <v>4.92</v>
       </c>
       <c r="X7" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="Z7" t="n">
         <v>2.33</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AC7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AI7" t="n">
         <v>2.46</v>
       </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AJ7" t="n">
-        <v>2.93</v>
+        <v>3.22</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
@@ -1535,13 +1535,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>6.3</v>
+        <v>8.5</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="N8" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="O8" t="n">
         <v>2.88</v>
@@ -1553,41 +1553,41 @@
         <v>1.33</v>
       </c>
       <c r="R8" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="S8" t="n">
         <v>2.5</v>
       </c>
       <c r="T8" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="U8" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="V8" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="W8" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="X8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC8" t="n">
         <v>1.65</v>
       </c>
-      <c r="Y8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AD8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1599,19 +1599,19 @@
         </is>
       </c>
       <c r="AF8" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AH8" t="n">
-        <v>6.9</v>
+        <v>8.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.26</v>
+        <v>2.55</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1908,7 +1908,7 @@
         <v>1.95</v>
       </c>
       <c r="AO10" s="3" t="n">
-        <v>45883.625</v>
+        <v>45883.64583333334</v>
       </c>
     </row>
     <row r="11">
@@ -1958,13 +1958,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M11" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="N11" t="n">
-        <v>9</v>
+        <v>7.1</v>
       </c>
       <c r="O11" t="n">
         <v>1.36</v>
@@ -1988,19 +1988,19 @@
         <v>1.05</v>
       </c>
       <c r="V11" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="W11" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Z11" t="n">
         <v>3.4</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.45</v>
       </c>
       <c r="AA11" t="n">
         <v>1.3</v>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AI11" t="n">
         <v>2.38</v>
       </c>
       <c r="AJ11" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M12" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="N12" t="n">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="O12" t="n">
         <v>1.36</v>
@@ -2129,19 +2129,19 @@
         <v>1.05</v>
       </c>
       <c r="V12" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="W12" t="n">
-        <v>2.37</v>
+        <v>3.4</v>
       </c>
       <c r="X12" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AA12" t="n">
         <v>1.3</v>
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AG12" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AI12" t="n">
         <v>2.38</v>
       </c>
       <c r="AJ12" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.19</v>
+        <v>3.4</v>
       </c>
       <c r="M13" t="n">
-        <v>4.69</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="O13" t="n">
         <v>2.38</v>
@@ -2255,10 +2255,10 @@
         <v>1.57</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="R13" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="S13" t="n">
         <v>2.02</v>
@@ -2276,22 +2276,22 @@
         <v>5</v>
       </c>
       <c r="X13" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AG13" t="n">
         <v>1.29</v>
@@ -2313,10 +2313,10 @@
         <v>3.75</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.63</v>
+        <v>2.49</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -689,83 +689,83 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.97</v>
+        <v>2.1</v>
       </c>
       <c r="M2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AH2" t="n">
         <v>2.7</v>
       </c>
-      <c r="N2" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>3.45</v>
-      </c>
       <c r="AI2" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
@@ -774,10 +774,10 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AO2" s="3" t="n">
         <v>45883.5</v>
@@ -945,25 +945,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -971,58 +971,58 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>3.58</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="R4" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="S4" t="n">
-        <v>2.65</v>
+        <v>2.95</v>
       </c>
       <c r="T4" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="U4" t="n">
         <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="W4" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="X4" t="n">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.4</v>
+        <v>3.88</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
@@ -1031,23 +1031,23 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2']</t>
         </is>
       </c>
       <c r="AF4" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.64</v>
+        <v>1.42</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3.8</v>
+        <v>2.96</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
@@ -1056,10 +1056,10 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AN4" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AO4" s="3" t="n">
         <v>45883.5</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1086,25 +1086,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1112,58 +1112,58 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.35</v>
+        <v>2.97</v>
       </c>
       <c r="M5" t="n">
-        <v>3.58</v>
+        <v>2.7</v>
       </c>
       <c r="N5" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="O5" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="R5" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="S5" t="n">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="T5" t="n">
         <v>1.32</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="V5" t="n">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="W5" t="n">
-        <v>2.95</v>
+        <v>2.25</v>
       </c>
       <c r="X5" t="n">
-        <v>2.11</v>
+        <v>2.75</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.88</v>
+        <v>4.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
@@ -1172,23 +1172,23 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF5" t="n">
         <v>1.4</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.96</v>
+        <v>3.45</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
@@ -1197,10 +1197,10 @@
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AO5" s="3" t="n">
         <v>45883.5</v>
@@ -1377,20 +1377,20 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['40', '88']</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -1518,20 +1518,20 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1590,12 +1590,12 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['41']</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['29']</t>
         </is>
       </c>
       <c r="AF8" t="n">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,95 +2381,95 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="M14" t="n">
-        <v>2.85</v>
+        <v>3.21</v>
       </c>
       <c r="N14" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="O14" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="P14" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="Q14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AN14" t="n">
         <v>1.67</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>4</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.73</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45883.89583333334</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,83 +2522,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.91</v>
+        <v>4.1</v>
       </c>
       <c r="M15" t="n">
-        <v>3.21</v>
+        <v>2.85</v>
       </c>
       <c r="N15" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="O15" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="P15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q15" t="n">
         <v>1.67</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Y15" t="n">
         <v>1.44</v>
       </c>
-      <c r="R15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.72</v>
-      </c>
       <c r="Z15" t="n">
-        <v>4.33</v>
+        <v>6.25</v>
       </c>
       <c r="AA15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.2</v>
       </c>
-      <c r="AB15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH15" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45883.89583333334</v>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -804,25 +804,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -830,83 +830,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.78</v>
+        <v>2.97</v>
       </c>
       <c r="M3" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="N3" t="n">
-        <v>1.99</v>
+        <v>2.39</v>
       </c>
       <c r="O3" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="P3" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S3" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="T3" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="V3" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="X3" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.5</v>
+        <v>2.07</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>['90+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['5', '45+6']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF3" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
@@ -915,10 +915,10 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AO3" s="3" t="n">
         <v>45883.5</v>
@@ -1086,25 +1086,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1112,83 +1112,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.97</v>
+        <v>2.78</v>
       </c>
       <c r="M5" t="n">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="N5" t="n">
-        <v>2.39</v>
+        <v>1.99</v>
       </c>
       <c r="O5" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="P5" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S5" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="T5" t="n">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="U5" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="W5" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.07</v>
+        <v>2.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+1']</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5', '45+6']</t>
         </is>
       </c>
       <c r="AF5" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AJ5" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
@@ -1197,10 +1197,10 @@
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AO5" s="3" t="n">
         <v>45883.5</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['83']</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -1803,17 +1803,17 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['12', '52', '87']</t>
         </is>
       </c>
       <c r="AF10" t="n">

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -794,7 +794,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -804,25 +804,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -830,58 +830,58 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.97</v>
+        <v>2.35</v>
       </c>
       <c r="M3" t="n">
-        <v>2.7</v>
+        <v>3.58</v>
       </c>
       <c r="N3" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="O3" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="P3" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="S3" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="T3" t="n">
         <v>1.32</v>
       </c>
       <c r="U3" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.55</v>
+        <v>1.32</v>
       </c>
       <c r="W3" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="X3" t="n">
-        <v>2.75</v>
+        <v>2.11</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.7</v>
+        <v>3.88</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
@@ -890,23 +890,23 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2']</t>
         </is>
       </c>
       <c r="AF3" t="n">
         <v>1.4</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3.45</v>
+        <v>2.96</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
@@ -915,10 +915,10 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AO3" s="3" t="n">
         <v>45883.5</v>
@@ -935,7 +935,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -945,25 +945,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -971,95 +971,95 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.35</v>
+        <v>2.78</v>
       </c>
       <c r="M4" t="n">
-        <v>3.58</v>
+        <v>2.77</v>
       </c>
       <c r="N4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB4" t="n">
         <v>2.5</v>
       </c>
-      <c r="O4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AC4" t="n">
-        <v>1.77</v>
+        <v>1.44</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+1']</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['2']</t>
+          <t>['5', '45+6']</t>
         </is>
       </c>
       <c r="AF4" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AG4" t="n">
         <v>1.42</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="AI4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AN4" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.8</v>
       </c>
       <c r="AO4" s="3" t="n">
         <v>45883.5</v>
@@ -1086,25 +1086,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1112,83 +1112,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.78</v>
+        <v>2.97</v>
       </c>
       <c r="M5" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="N5" t="n">
-        <v>1.99</v>
+        <v>2.39</v>
       </c>
       <c r="O5" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="P5" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S5" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="T5" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="U5" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="V5" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="X5" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.5</v>
+        <v>2.07</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>['90+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['5', '45+6']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF5" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AJ5" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
@@ -1197,10 +1197,10 @@
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AN5" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AO5" s="3" t="n">
         <v>45883.5</v>
@@ -1932,19 +1932,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+8']</t>
         </is>
       </c>
       <c r="AF11" t="n">
@@ -2082,20 +2082,20 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['1']</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="N13" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="O13" t="n">
         <v>2.38</v>
@@ -2255,7 +2255,7 @@
         <v>1.57</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="R13" t="n">
         <v>4.33</v>
@@ -2285,13 +2285,13 @@
         <v>2.04</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.68</v>
+        <v>1.93</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2304,19 +2304,19 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AH13" t="n">
         <v>3.75</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,83 +2381,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.91</v>
+        <v>4.1</v>
       </c>
       <c r="M14" t="n">
-        <v>3.21</v>
+        <v>2.85</v>
       </c>
       <c r="N14" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="O14" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="P14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q14" t="n">
         <v>1.67</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Y14" t="n">
         <v>1.44</v>
       </c>
-      <c r="R14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.72</v>
-      </c>
       <c r="Z14" t="n">
-        <v>4.33</v>
+        <v>6.25</v>
       </c>
       <c r="AA14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.2</v>
       </c>
-      <c r="AB14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH14" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45883.89583333334</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,95 +2522,95 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="M15" t="n">
-        <v>2.85</v>
+        <v>3.21</v>
       </c>
       <c r="N15" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="O15" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="P15" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="Q15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AN15" t="n">
         <v>1.67</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>4</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.73</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45883.89583333334</v>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO16"/>
+  <dimension ref="A1:AK16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,130 +513,110 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>Odd_D_HT</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>Odd_A_HT</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Over05</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Under05</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Over15</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Under15</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>FT_Odd_Over05</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over15</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under15</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over25</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under25</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over35</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under35</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_Yes</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_No</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>homeGoals</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>awayGoals</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Odd_H_D</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Odd_A_D</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_H_HT1</t>
-        </is>
-      </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Odd_D_HT1</t>
+          <t>Odd_marcar_prim_H</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>Odd_A_HT1</t>
+          <t>Odd_marcar_prim_A</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_DNB_H</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_DNB_A</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_marcar_prim_H</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_marcar_prim_A</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -653,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -663,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -689,97 +669,85 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.1</v>
+        <v>2.97</v>
       </c>
       <c r="M2" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>2.39</v>
       </c>
       <c r="O2" t="n">
-        <v>1.91</v>
+        <v>3.45</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.37</v>
+        <v>3.45</v>
       </c>
       <c r="R2" t="n">
-        <v>2.9</v>
+        <v>1.52</v>
       </c>
       <c r="S2" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.36</v>
+        <v>3.5</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="V2" t="n">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="W2" t="n">
-        <v>3.5</v>
+        <v>1.55</v>
       </c>
       <c r="X2" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.81</v>
+        <v>2.75</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.4</v>
+        <v>1.33</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.28</v>
+        <v>4.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.71</v>
+        <v>1.14</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD2" t="inlineStr">
+        <v>2.07</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF2" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AG2" t="n">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO2" s="3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK2" s="3" t="n">
         <v>45883.5</v>
       </c>
     </row>
@@ -804,25 +772,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -830,97 +798,85 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="M3" t="n">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="R3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T3" t="n">
         <v>2.65</v>
       </c>
-      <c r="S3" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.32</v>
-      </c>
       <c r="U3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V3" t="n">
         <v>1.01</v>
       </c>
-      <c r="V3" t="n">
-        <v>1.32</v>
-      </c>
       <c r="W3" t="n">
-        <v>2.95</v>
+        <v>1.27</v>
       </c>
       <c r="X3" t="n">
-        <v>2.11</v>
+        <v>3.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.88</v>
+        <v>1.81</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.18</v>
+        <v>3.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.93</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD3" t="inlineStr">
+        <v>1.71</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE3" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>['2']</t>
-        </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.4</v>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.3</v>
+        <v>1.64</v>
       </c>
       <c r="AI3" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AO3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK3" s="3" t="n">
         <v>45883.5</v>
       </c>
     </row>
@@ -980,88 +936,76 @@
         <v>1.99</v>
       </c>
       <c r="O4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>['90+1']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>['5', '45+6']</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI4" t="n">
         <v>2.6</v>
       </c>
-      <c r="P4" t="n">
+      <c r="AJ4" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2</v>
-      </c>
-      <c r="X4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>['90+1']</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>['5', '45+6']</t>
-        </is>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AO4" s="3" t="n">
+      <c r="AK4" s="3" t="n">
         <v>45883.5</v>
       </c>
     </row>
@@ -1076,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1086,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1112,97 +1056,85 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.97</v>
+        <v>2.35</v>
       </c>
       <c r="M5" t="n">
-        <v>2.7</v>
+        <v>3.58</v>
       </c>
       <c r="N5" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="O5" t="n">
-        <v>2.45</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.52</v>
+        <v>2.96</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="S5" t="n">
-        <v>3.5</v>
+        <v>2.65</v>
       </c>
       <c r="T5" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U5" t="n">
         <v>1.32</v>
       </c>
-      <c r="U5" t="n">
-        <v>1.12</v>
-      </c>
       <c r="V5" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>2.25</v>
+        <v>1.32</v>
       </c>
       <c r="X5" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.33</v>
+        <v>2.11</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.7</v>
+        <v>1.65</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.14</v>
+        <v>3.88</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.07</v>
+        <v>1.18</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD5" t="inlineStr">
+        <v>1.93</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE5" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.4</v>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>['2']</t>
+        </is>
       </c>
       <c r="AG5" t="n">
         <v>1.4</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.45</v>
+        <v>1.42</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AJ5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AO5" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK5" s="3" t="n">
         <v>45883.5</v>
       </c>
     </row>
@@ -1262,88 +1194,76 @@
         <v>8.5</v>
       </c>
       <c r="O6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>['68', '82', '90']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>['20']</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AI6" t="n">
         <v>1.4</v>
       </c>
-      <c r="P6" t="n">
+      <c r="AJ6" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="R6" t="n">
-        <v>4</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>['68', '82', '90']</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>['20']</t>
-        </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AO6" s="3" t="n">
+      <c r="AK6" s="3" t="n">
         <v>45883.52083333334</v>
       </c>
     </row>
@@ -1403,88 +1323,76 @@
         <v>2.82</v>
       </c>
       <c r="O7" t="n">
-        <v>1.8</v>
+        <v>2.77</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>2.46</v>
       </c>
       <c r="Q7" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="R7" t="n">
         <v>1.25</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>3.34</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>2.31</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>1.55</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>1.03</v>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>1.18</v>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>4.92</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Y7" t="n">
         <v>1.6</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>2.26</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AA7" t="n">
         <v>2.33</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.5</v>
       </c>
       <c r="AB7" t="n">
         <v>1.5</v>
       </c>
       <c r="AC7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD7" t="n">
         <v>2.4</v>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>['40', '88']</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF7" t="n">
+      <c r="AG7" t="n">
         <v>1.35</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AH7" t="n">
         <v>1.48</v>
       </c>
-      <c r="AH7" t="n">
-        <v>2.77</v>
-      </c>
       <c r="AI7" t="n">
-        <v>2.46</v>
+        <v>1.8</v>
       </c>
       <c r="AJ7" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AN7" t="n">
         <v>2</v>
       </c>
-      <c r="AO7" s="3" t="n">
+      <c r="AK7" s="3" t="n">
         <v>45883.60416666666</v>
       </c>
     </row>
@@ -1544,88 +1452,76 @@
         <v>1.28</v>
       </c>
       <c r="O8" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>['41']</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>['29']</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AI8" t="n">
         <v>2.88</v>
       </c>
-      <c r="P8" t="n">
+      <c r="AJ8" t="n">
         <v>1.44</v>
       </c>
-      <c r="Q8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="R8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>['41']</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>['29']</t>
-        </is>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AO8" s="3" t="n">
+      <c r="AK8" s="3" t="n">
         <v>45883.61458333334</v>
       </c>
     </row>
@@ -1685,88 +1581,76 @@
         <v>9.4</v>
       </c>
       <c r="O9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD9" t="n">
         <v>1.38</v>
       </c>
-      <c r="P9" t="n">
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>['83']</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>3.9</v>
       </c>
-      <c r="Q9" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>['83']</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>7.43</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AO9" s="3" t="n">
+      <c r="AK9" s="3" t="n">
         <v>45883.625</v>
       </c>
     </row>
@@ -1826,88 +1710,76 @@
         <v>1.98</v>
       </c>
       <c r="O10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>['12', '52', '87']</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI10" t="n">
         <v>2.55</v>
       </c>
-      <c r="P10" t="n">
+      <c r="AJ10" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="W10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>['12', '52', '87']</t>
-        </is>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO10" s="3" t="n">
+      <c r="AK10" s="3" t="n">
         <v>45883.64583333334</v>
       </c>
     </row>
@@ -1932,23 +1804,23 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
         <v>1</v>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
@@ -1958,97 +1830,85 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="N11" t="n">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="O11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>8</v>
+      </c>
+      <c r="R11" t="n">
         <v>1.36</v>
       </c>
-      <c r="P11" t="n">
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>['1']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>3.5</v>
       </c>
-      <c r="Q11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="R11" t="n">
-        <v>3</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W11" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>['90+8']</t>
-        </is>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AO11" s="3" t="n">
+      <c r="AK11" s="3" t="n">
         <v>45883.79166666666</v>
       </c>
     </row>
@@ -2073,22 +1933,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
         <v>1</v>
       </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -2099,97 +1959,85 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N12" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U12" t="n">
         <v>1.4</v>
       </c>
-      <c r="M12" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="N12" t="n">
-        <v>9</v>
-      </c>
-      <c r="O12" t="n">
+      <c r="V12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>['90+8']</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI12" t="n">
         <v>1.36</v>
       </c>
-      <c r="P12" t="n">
+      <c r="AJ12" t="n">
         <v>3.5</v>
       </c>
-      <c r="Q12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="R12" t="n">
-        <v>3</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>['1']</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AO12" s="3" t="n">
+      <c r="AK12" s="3" t="n">
         <v>45883.79166666666</v>
       </c>
     </row>
@@ -2223,20 +2071,20 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -2249,88 +2097,76 @@
         <v>1.71</v>
       </c>
       <c r="O13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X13" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>['23', '87']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>['16', '41']</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI13" t="n">
         <v>2.38</v>
       </c>
-      <c r="P13" t="n">
+      <c r="AJ13" t="n">
         <v>1.57</v>
       </c>
-      <c r="Q13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="R13" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W13" t="n">
-        <v>5</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AO13" s="3" t="n">
+      <c r="AK13" s="3" t="n">
         <v>45883.83333333334</v>
       </c>
     </row>
@@ -2355,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2377,101 +2213,89 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="M14" t="n">
-        <v>2.85</v>
+        <v>3.21</v>
       </c>
       <c r="N14" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="O14" t="n">
-        <v>2.75</v>
+        <v>4.75</v>
       </c>
       <c r="P14" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>1.67</v>
       </c>
-      <c r="R14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>4</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AO14" s="3" t="n">
+      <c r="AK14" s="3" t="n">
         <v>45883.89583333334</v>
       </c>
     </row>
@@ -2496,123 +2320,111 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.91</v>
+        <v>4.1</v>
       </c>
       <c r="M15" t="n">
-        <v>3.21</v>
+        <v>2.85</v>
       </c>
       <c r="N15" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="O15" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="P15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R15" t="n">
         <v>1.67</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="S15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Z15" t="n">
         <v>1.44</v>
       </c>
-      <c r="R15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4.33</v>
-      </c>
       <c r="AA15" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>['7', '12', '30', '75']</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1.2</v>
       </c>
-      <c r="AB15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>4.75</v>
-      </c>
       <c r="AI15" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO15" s="3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK15" s="3" t="n">
         <v>45883.89583333334</v>
       </c>
     </row>
@@ -2646,114 +2458,102 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="M16" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>['77']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>['18', '88']</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>2.62</v>
       </c>
-      <c r="N16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="S16" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>6.91</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AO16" s="3" t="n">
+      <c r="AK16" s="3" t="n">
         <v>45883.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-08-14.xlsx
+++ b/jogos_2025-08-14.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.97</v>
+        <v>2.1</v>
       </c>
       <c r="M2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O2" t="n">
         <v>2.7</v>
       </c>
-      <c r="N2" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="O2" t="n">
-        <v>3.45</v>
-      </c>
       <c r="P2" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="R2" t="n">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="T2" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X2" t="n">
         <v>3.5</v>
       </c>
-      <c r="U2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Y2" t="n">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.33</v>
+        <v>1.81</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.07</v>
+        <v>1.71</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45883.5</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,25 +772,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S3" t="n">
         <v>2.1</v>
       </c>
-      <c r="M3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.9</v>
-      </c>
       <c r="T3" t="n">
-        <v>2.65</v>
+        <v>4.5</v>
       </c>
       <c r="U3" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="W3" t="n">
-        <v>1.27</v>
+        <v>1.7</v>
       </c>
       <c r="X3" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.95</v>
+        <v>3.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.81</v>
+        <v>1.28</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.28</v>
+        <v>1.09</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.71</v>
+        <v>2.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+1']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5', '45+6']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.64</v>
+        <v>1.42</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45883.5</v>
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.78</v>
+        <v>2.97</v>
       </c>
       <c r="M4" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="N4" t="n">
-        <v>1.99</v>
+        <v>2.39</v>
       </c>
       <c r="O4" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="T4" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="U4" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.5</v>
+        <v>2.07</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['90+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>['5', '45+6']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45883.5</v>
@@ -2191,25 +2191,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.91</v>
+        <v>4.1</v>
       </c>
       <c r="M14" t="n">
-        <v>3.21</v>
+        <v>2.85</v>
       </c>
       <c r="N14" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="O14" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="P14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S14" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC14" t="n">
         <v>2.5</v>
       </c>
-      <c r="R14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB14" t="n">
+      <c r="AD14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>['7', '12', '30', '75']</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH14" t="n">
         <v>1.2</v>
       </c>
-      <c r="AC14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AI14" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45883.89583333334</v>
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="M15" t="n">
-        <v>2.85</v>
+        <v>3.21</v>
       </c>
       <c r="N15" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="O15" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="P15" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="R15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.67</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>4</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>['7', '12', '30', '75']</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.73</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45883.89583333334</v>
